--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/Pycharm/MAWM/J30/Classes_and_files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/Pycharm/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD779C7-75B3-9B43-88ED-8849C00736EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06811CAB-4B34-8F4B-A813-289B0CF75A1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="880" windowWidth="52440" windowHeight="22500" xr2:uid="{42CC21F1-E411-8B4E-AF9F-23E71D9E71DE}"/>
+    <workbookView xWindow="36640" yWindow="7040" windowWidth="36000" windowHeight="22500" xr2:uid="{42CC21F1-E411-8B4E-AF9F-23E71D9E71DE}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateASN" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="ItemSearch" sheetId="3" r:id="rId3"/>
     <sheet name="GoodsHolderAnnounced" sheetId="4" r:id="rId4"/>
     <sheet name="GoodsHolderWeighed" sheetId="5" r:id="rId5"/>
+    <sheet name="InboundMaster" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -83,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="39">
   <si>
     <t>Item</t>
   </si>
@@ -121,9 +122,6 @@
     <t>Search_by_Missing_Dims</t>
   </si>
   <si>
-    <t>203040-001-MISC</t>
-  </si>
-  <si>
     <t>6</t>
   </si>
   <si>
@@ -136,22 +134,73 @@
     <t>Apparel</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
     <t>Origin Facility</t>
   </si>
   <si>
     <t>0005005401</t>
   </si>
   <si>
-    <t>VASN1207QA67990</t>
-  </si>
-  <si>
     <t>12</t>
   </si>
   <si>
-    <t>DEV</t>
+    <t>Carrier</t>
+  </si>
+  <si>
+    <t>AUPU</t>
+  </si>
+  <si>
+    <t>JVQ250714100007</t>
+  </si>
+  <si>
+    <t>Equipment</t>
+  </si>
+  <si>
+    <t>Footwear</t>
+  </si>
+  <si>
+    <t>CreateASN</t>
+  </si>
+  <si>
+    <t>InboundDelivery</t>
+  </si>
+  <si>
+    <t>GHAnnounced</t>
+  </si>
+  <si>
+    <t>GHWeighed</t>
+  </si>
+  <si>
+    <t>PutawayComplete</t>
+  </si>
+  <si>
+    <t>RunAll</t>
+  </si>
+  <si>
+    <t>924156-100-S;420420-420-M;DD9293-100-7</t>
+  </si>
+  <si>
+    <t>924156-100-S;DD9293-100-7</t>
+  </si>
+  <si>
+    <t>924156-100-S</t>
+  </si>
+  <si>
+    <t>DD9293-100-7</t>
+  </si>
+  <si>
+    <t>420420-420-M</t>
+  </si>
+  <si>
+    <t>12;12;12</t>
+  </si>
+  <si>
+    <t>6;6;6</t>
+  </si>
+  <si>
+    <t>12;12</t>
+  </si>
+  <si>
+    <t>6;6</t>
   </si>
 </sst>
 </file>
@@ -557,7 +606,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAFEB96B-A165-0D40-BEA2-4B797ACC428A}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
@@ -568,7 +617,7 @@
     <col min="7" max="7" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -588,36 +637,154 @@
         <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1081</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1081</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>1081</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>19</v>
+      <c r="G4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>1081</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>1081</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" display="12@12;12" xr:uid="{FA5437EE-EDA0-7E4D-8791-CF298EFA052E}"/>
     <hyperlink ref="F2" r:id="rId2" display="6@6;6" xr:uid="{00604A3B-6BC0-C148-8CF3-A87D410A5D75}"/>
+    <hyperlink ref="E3" r:id="rId3" display="12@12;12" xr:uid="{5CD5436D-D223-B944-8A2D-1B3A7CA7AA49}"/>
+    <hyperlink ref="F3" r:id="rId4" display="6@6;6" xr:uid="{DAFEDD3C-8D4A-7F4C-8EC9-108E92D7056F}"/>
+    <hyperlink ref="E4" r:id="rId5" display="12@12;12" xr:uid="{E3D29B3D-B0E6-6D47-BF22-A612F26DFD43}"/>
+    <hyperlink ref="F4" r:id="rId6" display="6@6;6" xr:uid="{16C561DF-6848-3B40-AD80-9D3FF3FE04A2}"/>
+    <hyperlink ref="E5" r:id="rId7" display="12@12;12" xr:uid="{AD02AC81-96A3-9846-B74C-15B5E7FDF760}"/>
+    <hyperlink ref="F5" r:id="rId8" display="6@6;6" xr:uid="{70C877F0-2C90-A243-AC86-6762ABAA9A0D}"/>
+    <hyperlink ref="E6" r:id="rId9" display="12@12;12" xr:uid="{0EDB2743-F3C8-0E49-909A-5EC31F811AC3}"/>
+    <hyperlink ref="F6" r:id="rId10" display="6@6;6" xr:uid="{18FB1008-07E0-5C46-8F7F-496B13292E2B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -652,7 +819,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -662,7 +829,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B9183DE-D7AA-DE46-A3B4-9DCF4B2521A8}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="21.83203125" bestFit="1" customWidth="1"/>
@@ -703,10 +870,35 @@
         <v>3</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" t="s">
-        <v>17</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1081</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>1081</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -737,7 +929,7 @@
         <v>7</v>
       </c>
       <c r="D1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -748,7 +940,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -793,7 +985,7 @@
         <v>7</v>
       </c>
       <c r="D1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -802,6 +994,43 @@
       </c>
       <c r="B2" t="s">
         <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAD0A41D-4930-B447-B269-74D79A2958B3}">
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/Pycharm/Nike/J30/Input_files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06811CAB-4B34-8F4B-A813-289B0CF75A1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43683E86-0A79-E747-B919-6738E4A2176B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36640" yWindow="7040" windowWidth="36000" windowHeight="22500" xr2:uid="{42CC21F1-E411-8B4E-AF9F-23E71D9E71DE}"/>
+    <workbookView xWindow="36640" yWindow="6300" windowWidth="36000" windowHeight="22500" xr2:uid="{42CC21F1-E411-8B4E-AF9F-23E71D9E71DE}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateASN" sheetId="1" r:id="rId1"/>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="31">
   <si>
     <t>Item</t>
   </si>
@@ -176,31 +176,7 @@
     <t>RunAll</t>
   </si>
   <si>
-    <t>924156-100-S;420420-420-M;DD9293-100-7</t>
-  </si>
-  <si>
-    <t>924156-100-S;DD9293-100-7</t>
-  </si>
-  <si>
-    <t>924156-100-S</t>
-  </si>
-  <si>
-    <t>DD9293-100-7</t>
-  </si>
-  <si>
     <t>420420-420-M</t>
-  </si>
-  <si>
-    <t>12;12;12</t>
-  </si>
-  <si>
-    <t>6;6;6</t>
-  </si>
-  <si>
-    <t>12;12</t>
-  </si>
-  <si>
-    <t>6;6</t>
   </si>
 </sst>
 </file>
@@ -264,11 +240,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
@@ -606,7 +581,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAFEB96B-A165-0D40-BEA2-4B797ACC428A}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
@@ -653,138 +628,26 @@
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>1081</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>1081</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>1081</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>1081</v>
-      </c>
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" t="s">
-        <v>20</v>
-      </c>
-    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" display="12@12;12" xr:uid="{FA5437EE-EDA0-7E4D-8791-CF298EFA052E}"/>
-    <hyperlink ref="F2" r:id="rId2" display="6@6;6" xr:uid="{00604A3B-6BC0-C148-8CF3-A87D410A5D75}"/>
-    <hyperlink ref="E3" r:id="rId3" display="12@12;12" xr:uid="{5CD5436D-D223-B944-8A2D-1B3A7CA7AA49}"/>
-    <hyperlink ref="F3" r:id="rId4" display="6@6;6" xr:uid="{DAFEDD3C-8D4A-7F4C-8EC9-108E92D7056F}"/>
-    <hyperlink ref="E4" r:id="rId5" display="12@12;12" xr:uid="{E3D29B3D-B0E6-6D47-BF22-A612F26DFD43}"/>
-    <hyperlink ref="F4" r:id="rId6" display="6@6;6" xr:uid="{16C561DF-6848-3B40-AD80-9D3FF3FE04A2}"/>
-    <hyperlink ref="E5" r:id="rId7" display="12@12;12" xr:uid="{AD02AC81-96A3-9846-B74C-15B5E7FDF760}"/>
-    <hyperlink ref="F5" r:id="rId8" display="6@6;6" xr:uid="{70C877F0-2C90-A243-AC86-6762ABAA9A0D}"/>
-    <hyperlink ref="E6" r:id="rId9" display="12@12;12" xr:uid="{0EDB2743-F3C8-0E49-909A-5EC31F811AC3}"/>
-    <hyperlink ref="F6" r:id="rId10" display="6@6;6" xr:uid="{18FB1008-07E0-5C46-8F7F-496B13292E2B}"/>
+    <hyperlink ref="E2" r:id="rId1" display="12@12;12" xr:uid="{0EDB2743-F3C8-0E49-909A-5EC31F811AC3}"/>
+    <hyperlink ref="F2" r:id="rId2" display="6@6;6" xr:uid="{18FB1008-07E0-5C46-8F7F-496B13292E2B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -944,19 +807,19 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="D3" s="4"/>
+      <c r="D3" s="3"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="D4" s="4"/>
+      <c r="D4" s="3"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="D5" s="4"/>
+      <c r="D5" s="3"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="D6" s="4"/>
+      <c r="D6" s="3"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="D7" s="4"/>
+      <c r="D7" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -8,17 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43683E86-0A79-E747-B919-6738E4A2176B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02C8BBCF-F3AD-6240-BB5A-C4954342BFDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36640" yWindow="6300" windowWidth="36000" windowHeight="22500" xr2:uid="{42CC21F1-E411-8B4E-AF9F-23E71D9E71DE}"/>
+    <workbookView xWindow="14820" yWindow="1880" windowWidth="45300" windowHeight="22500" activeTab="4" xr2:uid="{42CC21F1-E411-8B4E-AF9F-23E71D9E71DE}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateASN" sheetId="1" r:id="rId1"/>
     <sheet name="SearchASN" sheetId="2" r:id="rId2"/>
     <sheet name="ItemSearch" sheetId="3" r:id="rId3"/>
     <sheet name="GoodsHolderAnnounced" sheetId="4" r:id="rId4"/>
-    <sheet name="GoodsHolderWeighed" sheetId="5" r:id="rId5"/>
-    <sheet name="InboundMaster" sheetId="6" r:id="rId6"/>
+    <sheet name="PutawayTaskComplete" sheetId="8" r:id="rId5"/>
+    <sheet name="GoodsHolderWeighed" sheetId="5" r:id="rId6"/>
+    <sheet name="InboundMaster" sheetId="6" r:id="rId7"/>
+    <sheet name="BackUP" sheetId="7" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -84,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="38">
   <si>
     <t>Item</t>
   </si>
@@ -128,9 +130,6 @@
     <t>LPNID</t>
   </si>
   <si>
-    <t>0000VG09072025QA22330000</t>
-  </si>
-  <si>
     <t>Apparel</t>
   </si>
   <si>
@@ -140,43 +139,67 @@
     <t>0005005401</t>
   </si>
   <si>
+    <t>Carrier</t>
+  </si>
+  <si>
+    <t>AUPU</t>
+  </si>
+  <si>
+    <t>Equipment</t>
+  </si>
+  <si>
+    <t>Footwear</t>
+  </si>
+  <si>
+    <t>CreateASN</t>
+  </si>
+  <si>
+    <t>InboundDelivery</t>
+  </si>
+  <si>
+    <t>GHAnnounced</t>
+  </si>
+  <si>
+    <t>GHWeighed</t>
+  </si>
+  <si>
+    <t>PutawayComplete</t>
+  </si>
+  <si>
+    <t>RunAll</t>
+  </si>
+  <si>
+    <t>924156-100-S;420420-420-M;DD9293-100-7</t>
+  </si>
+  <si>
+    <t>6;6</t>
+  </si>
+  <si>
+    <t>6;6;6</t>
+  </si>
+  <si>
+    <t>924156-100-S;DD9293-100-7</t>
+  </si>
+  <si>
+    <t>924156-100-S</t>
+  </si>
+  <si>
+    <t>DD9293-100-7</t>
+  </si>
+  <si>
+    <t>S575093274</t>
+  </si>
+  <si>
     <t>12</t>
   </si>
   <si>
-    <t>Carrier</t>
-  </si>
-  <si>
-    <t>AUPU</t>
-  </si>
-  <si>
-    <t>JVQ250714100007</t>
-  </si>
-  <si>
-    <t>Equipment</t>
-  </si>
-  <si>
-    <t>Footwear</t>
-  </si>
-  <si>
-    <t>CreateASN</t>
-  </si>
-  <si>
-    <t>InboundDelivery</t>
-  </si>
-  <si>
-    <t>GHAnnounced</t>
-  </si>
-  <si>
-    <t>GHWeighed</t>
-  </si>
-  <si>
-    <t>PutawayComplete</t>
-  </si>
-  <si>
-    <t>RunAll</t>
-  </si>
-  <si>
-    <t>420420-420-M</t>
+    <t>AC4081-014-MISC</t>
+  </si>
+  <si>
+    <t>0000VG16072025QA71880000;0000VG16072025QA89280001</t>
+  </si>
+  <si>
+    <t>0000VG16072025QA71880000;00000000108101023408</t>
   </si>
 </sst>
 </file>
@@ -581,12 +604,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAFEB96B-A165-0D40-BEA2-4B797ACC428A}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="48.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="51.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -612,10 +635,10 @@
         <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -629,26 +652,33 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" t="s">
-        <v>20</v>
-      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="4"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G4" s="4"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G5" s="4"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" display="12@12;12" xr:uid="{0EDB2743-F3C8-0E49-909A-5EC31F811AC3}"/>
-    <hyperlink ref="F2" r:id="rId2" display="6@6;6" xr:uid="{18FB1008-07E0-5C46-8F7F-496B13292E2B}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -682,7 +712,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -733,7 +763,7 @@
         <v>3</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -747,7 +777,7 @@
         <v>3</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -761,7 +791,7 @@
         <v>3</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -803,7 +833,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -827,6 +857,44 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C28F16B0-DC10-294B-ABB9-7C124875B13D}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="47.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1081</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A3C3BB5-2CD4-434E-8D5E-3EF32DB5E8EC}">
   <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -858,13 +926,16 @@
       <c r="B2" t="s">
         <v>6</v>
       </c>
+      <c r="D2" t="s">
+        <v>36</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAD0A41D-4930-B447-B269-74D79A2958B3}">
   <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -878,25 +949,146 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" t="s">
         <v>24</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E1" t="s">
         <v>25</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>26</v>
-      </c>
-      <c r="D1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{594297BC-D256-A64D-9D4F-D6CE762B919E}">
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="38.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1">
+        <v>1081</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1081</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1081</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>1081</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F1" r:id="rId1" display="6@6;6" xr:uid="{18FB1008-07E0-5C46-8F7F-496B13292E2B}"/>
+    <hyperlink ref="E1" r:id="rId2" display="6@6;6" xr:uid="{06896637-CD23-B347-9B8A-8AE6C644740F}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02C8BBCF-F3AD-6240-BB5A-C4954342BFDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B3CAD6B-BFFE-F94D-BA77-3E328D2AD949}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14820" yWindow="1880" windowWidth="45300" windowHeight="22500" activeTab="4" xr2:uid="{42CC21F1-E411-8B4E-AF9F-23E71D9E71DE}"/>
+    <workbookView xWindow="45360" yWindow="2860" windowWidth="34160" windowHeight="20800" xr2:uid="{42CC21F1-E411-8B4E-AF9F-23E71D9E71DE}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateASN" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,8 @@
     <sheet name="PutawayTaskComplete" sheetId="8" r:id="rId5"/>
     <sheet name="GoodsHolderWeighed" sheetId="5" r:id="rId6"/>
     <sheet name="InboundMaster" sheetId="6" r:id="rId7"/>
-    <sheet name="BackUP" sheetId="7" r:id="rId8"/>
+    <sheet name="Sheet1" sheetId="9" r:id="rId8"/>
+    <sheet name="BackUP" sheetId="7" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -86,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="39">
   <si>
     <t>Item</t>
   </si>
@@ -187,19 +188,22 @@
     <t>DD9293-100-7</t>
   </si>
   <si>
-    <t>S575093274</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>AC4081-014-MISC</t>
-  </si>
-  <si>
     <t>0000VG16072025QA71880000;0000VG16072025QA89280001</t>
   </si>
   <si>
-    <t>0000VG16072025QA71880000;00000000108101023408</t>
+    <t xml:space="preserve">AZ76410338 </t>
+  </si>
+  <si>
+    <t>VASN1707QA8841;VASN1707QA5060</t>
+  </si>
+  <si>
+    <t>DC2380-447-4</t>
+  </si>
+  <si>
+    <t>924156-100-S@420420-420-M;DD9293-100-7</t>
+  </si>
+  <si>
+    <t>6@6;6</t>
   </si>
 </sst>
 </file>
@@ -652,10 +656,10 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>12</v>
@@ -668,9 +672,30 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="4"/>
+      <c r="A3">
+        <v>1081</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="G4" s="4"/>
@@ -679,6 +704,11 @@
       <c r="G5" s="4"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F3" r:id="rId1" xr:uid="{C8576122-EF95-ED4A-8184-0BBE28B263F5}"/>
+    <hyperlink ref="E3" r:id="rId2" xr:uid="{C4FF4CE7-4C59-7145-95A6-9D609DA55D26}"/>
+    <hyperlink ref="D3" r:id="rId3" xr:uid="{12A824E3-E65C-7444-8EDE-6CB4FCD6CCBD}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -712,7 +742,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -833,7 +863,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -861,6 +891,7 @@
   <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="3" max="3" width="11.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="47.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -885,8 +916,8 @@
       <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
-        <v>37</v>
+      <c r="C2" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -927,7 +958,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -973,6 +1004,15 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDACA90B-83DF-9A42-BE03-ACEE1DCC82F3}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{594297BC-D256-A64D-9D4F-D6CE762B919E}">
   <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B3CAD6B-BFFE-F94D-BA77-3E328D2AD949}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4324F2F6-0F29-F946-A0DD-9B80A5FC339F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45360" yWindow="2860" windowWidth="34160" windowHeight="20800" xr2:uid="{42CC21F1-E411-8B4E-AF9F-23E71D9E71DE}"/>
+    <workbookView xWindow="700" yWindow="1880" windowWidth="36000" windowHeight="22500" xr2:uid="{42CC21F1-E411-8B4E-AF9F-23E71D9E71DE}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateASN" sheetId="1" r:id="rId1"/>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="39">
   <si>
     <t>Item</t>
   </si>
@@ -197,13 +197,13 @@
     <t>VASN1707QA8841;VASN1707QA5060</t>
   </si>
   <si>
-    <t>DC2380-447-4</t>
-  </si>
-  <si>
-    <t>924156-100-S@420420-420-M;DD9293-100-7</t>
-  </si>
-  <si>
-    <t>6@6;6</t>
+    <t>924156-100-S;DN0560-885-6</t>
+  </si>
+  <si>
+    <t>100;100</t>
+  </si>
+  <si>
+    <t>10;10</t>
   </si>
 </sst>
 </file>
@@ -608,7 +608,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAFEB96B-A165-0D40-BEA2-4B797ACC428A}">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
@@ -653,16 +653,16 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>36</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>16</v>
@@ -672,43 +672,12 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>1081</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" t="s">
-        <v>18</v>
-      </c>
+      <c r="G3" s="4"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G5" s="4"/>
-    </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="F3" r:id="rId1" xr:uid="{C8576122-EF95-ED4A-8184-0BBE28B263F5}"/>
-    <hyperlink ref="E3" r:id="rId2" xr:uid="{C4FF4CE7-4C59-7145-95A6-9D609DA55D26}"/>
-    <hyperlink ref="D3" r:id="rId3" xr:uid="{12A824E3-E65C-7444-8EDE-6CB4FCD6CCBD}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4324F2F6-0F29-F946-A0DD-9B80A5FC339F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BDA7695-B3AC-5E46-AE7B-0B8C10124141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="700" yWindow="1880" windowWidth="36000" windowHeight="22500" xr2:uid="{42CC21F1-E411-8B4E-AF9F-23E71D9E71DE}"/>
+    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" activeTab="4" xr2:uid="{42CC21F1-E411-8B4E-AF9F-23E71D9E71DE}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateASN" sheetId="1" r:id="rId1"/>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="40">
   <si>
     <t>Item</t>
   </si>
@@ -191,9 +191,6 @@
     <t>0000VG16072025QA71880000;0000VG16072025QA89280001</t>
   </si>
   <si>
-    <t xml:space="preserve">AZ76410338 </t>
-  </si>
-  <si>
     <t>VASN1707QA8841;VASN1707QA5060</t>
   </si>
   <si>
@@ -204,6 +201,12 @@
   </si>
   <si>
     <t>10;10</t>
+  </si>
+  <si>
+    <t>0000VG17072025QA76140000;0000VG17072025QA18580001;0000VG17072025QA27220002;0000VG17072025QA80720003;0000VG17072025QA27120004;0000VG17072025QA51610005;0000VG17072025QA95050006;0000VG17072025QA81350007;0000VG17072025QA60090008;0000VG17072025QA12260009;0000VG17072025QA89050010;0000VG17072025QA31840011;0000VG17072025QA66890012;0000VG17072025QA83900013;0000VG17072025QA20970014;0000VG17072025QA98670015;0000VG17072025QA75830016;0000VG17072025QA29240017;0000VG17072025QA33920018;0000VG17072025QA75940019;0000VG17072025QA36890020;0000VG17072025QA49070021;0000VG17072025QA33010022;0000VG17072025QA79000023;0000VG17072025QA78020024;0000VG17072025QA41630025;0000VG17072025QA51030026;0000VG17072025QA13970027;0000VG17072025QA75370028;0000VG17072025QA72270029</t>
+  </si>
+  <si>
+    <t>0000VG17072025QA18580001</t>
   </si>
 </sst>
 </file>
@@ -656,13 +659,13 @@
         <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>16</v>
@@ -711,7 +714,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -832,7 +835,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -885,8 +888,8 @@
       <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
-        <v>34</v>
+      <c r="D2" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4324F2F6-0F29-F946-A0DD-9B80A5FC339F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3551056A-3DA1-D947-9A03-4345E04180E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="700" yWindow="1880" windowWidth="36000" windowHeight="22500" xr2:uid="{42CC21F1-E411-8B4E-AF9F-23E71D9E71DE}"/>
+    <workbookView xWindow="36000" yWindow="3340" windowWidth="36000" windowHeight="22500" xr2:uid="{42CC21F1-E411-8B4E-AF9F-23E71D9E71DE}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateASN" sheetId="1" r:id="rId1"/>
@@ -18,9 +18,9 @@
     <sheet name="ItemSearch" sheetId="3" r:id="rId3"/>
     <sheet name="GoodsHolderAnnounced" sheetId="4" r:id="rId4"/>
     <sheet name="PutawayTaskComplete" sheetId="8" r:id="rId5"/>
-    <sheet name="GoodsHolderWeighed" sheetId="5" r:id="rId6"/>
-    <sheet name="InboundMaster" sheetId="6" r:id="rId7"/>
-    <sheet name="Sheet1" sheetId="9" r:id="rId8"/>
+    <sheet name="InboundDelivery" sheetId="10" r:id="rId6"/>
+    <sheet name="GoodsHolderWeighed" sheetId="5" r:id="rId7"/>
+    <sheet name="InboundMaster" sheetId="6" r:id="rId8"/>
     <sheet name="BackUP" sheetId="7" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="43">
   <si>
     <t>Item</t>
   </si>
@@ -191,19 +191,31 @@
     <t>0000VG16072025QA71880000;0000VG16072025QA89280001</t>
   </si>
   <si>
-    <t xml:space="preserve">AZ76410338 </t>
-  </si>
-  <si>
     <t>VASN1707QA8841;VASN1707QA5060</t>
   </si>
   <si>
-    <t>924156-100-S;DN0560-885-6</t>
-  </si>
-  <si>
-    <t>100;100</t>
-  </si>
-  <si>
-    <t>10;10</t>
+    <t>0000VG17072025QA76140000;0000VG17072025QA18580001;0000VG17072025QA27220002;0000VG17072025QA80720003;0000VG17072025QA27120004;0000VG17072025QA51610005;0000VG17072025QA95050006;0000VG17072025QA81350007;0000VG17072025QA60090008;0000VG17072025QA12260009;0000VG17072025QA89050010;0000VG17072025QA31840011;0000VG17072025QA66890012;0000VG17072025QA83900013;0000VG17072025QA20970014;0000VG17072025QA98670015;0000VG17072025QA75830016;0000VG17072025QA29240017;0000VG17072025QA33920018;0000VG17072025QA75940019;0000VG17072025QA36890020;0000VG17072025QA49070021;0000VG17072025QA33010022;0000VG17072025QA79000023;0000VG17072025QA78020024;0000VG17072025QA41630025;0000VG17072025QA51030026;0000VG17072025QA13970027;0000VG17072025QA75370028;0000VG17072025QA72270029</t>
+  </si>
+  <si>
+    <t>0000VG17072025QA27220002;0000VG17072025QA80720003;0000VG17072025QA27120004;0000VG17072025QA51610005;0000VG17072025QA95050006;0000VG17072025QA81350007;0000VG17072025QA60090008;0000VG17072025QA12260009;0000VG17072025QA89050010;0000VG17072025QA31840011;0000VG17072025QA66890012;0000VG17072025QA83900013;0000VG17072025QA20970014;0000VG17072025QA98670015;0000VG17072025QA75830016;0000VG17072025QA29240017;0000VG17072025QA33920018;0000VG17072025QA75940019;0000VG17072025QA36890020;0000VG17072025QA49070021;0000VG17072025QA33010022;0000VG17072025QA79000023;0000VG17072025QA78020024;0000VG17072025QA41630025;0000VG17072025QA51030026;0000VG17072025QA13970027;0000VG17072025QA75370028;0000VG17072025QA72270029</t>
+  </si>
+  <si>
+    <t>VGASNTEST;VGTEST01</t>
+  </si>
+  <si>
+    <t>Initial</t>
+  </si>
+  <si>
+    <t>JV</t>
+  </si>
+  <si>
+    <t>DC2380-447-4</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>PLUS</t>
   </si>
 </sst>
 </file>
@@ -608,18 +620,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAFEB96B-A165-0D40-BEA2-4B797ACC428A}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="51.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="51.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -627,55 +640,61 @@
         <v>5</v>
       </c>
       <c r="C1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1081</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2">
         <v>2</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G3" s="4"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G4" s="4"/>
+      <c r="I2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="H3" s="4"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="H4" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -711,7 +730,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -832,7 +851,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -885,8 +904,8 @@
       <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
-        <v>34</v>
+      <c r="D2" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -895,6 +914,41 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64A059F3-6E6F-6147-A5D8-D618E64F9347}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="19.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1081</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A3C3BB5-2CD4-434E-8D5E-3EF32DB5E8EC}">
   <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -935,7 +989,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAD0A41D-4930-B447-B269-74D79A2958B3}">
   <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -972,15 +1026,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDACA90B-83DF-9A42-BE03-ACEE1DCC82F3}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{594297BC-D256-A64D-9D4F-D6CE762B919E}">
   <dimension ref="A1:H4"/>

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10B247EF-190E-734D-AA3C-B48367DAA4E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96A7137D-370A-584A-96A4-0A3597B1474D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="68260" yWindow="500" windowWidth="34140" windowHeight="28300" activeTab="5" xr2:uid="{42CC21F1-E411-8B4E-AF9F-23E71D9E71DE}"/>
+    <workbookView xWindow="35120" yWindow="500" windowWidth="34140" windowHeight="28300" activeTab="1" xr2:uid="{42CC21F1-E411-8B4E-AF9F-23E71D9E71DE}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateASN" sheetId="1" r:id="rId1"/>
@@ -191,9 +191,6 @@
     <t>0000VG16072025QA71880000;0000VG16072025QA89280001</t>
   </si>
   <si>
-    <t>VASN1707QA8841;VASN1707QA5060</t>
-  </si>
-  <si>
     <t>0000VG17072025QA76140000;0000VG17072025QA18580001;0000VG17072025QA27220002;0000VG17072025QA80720003;0000VG17072025QA27120004;0000VG17072025QA51610005;0000VG17072025QA95050006;0000VG17072025QA81350007;0000VG17072025QA60090008;0000VG17072025QA12260009;0000VG17072025QA89050010;0000VG17072025QA31840011;0000VG17072025QA66890012;0000VG17072025QA83900013;0000VG17072025QA20970014;0000VG17072025QA98670015;0000VG17072025QA75830016;0000VG17072025QA29240017;0000VG17072025QA33920018;0000VG17072025QA75940019;0000VG17072025QA36890020;0000VG17072025QA49070021;0000VG17072025QA33010022;0000VG17072025QA79000023;0000VG17072025QA78020024;0000VG17072025QA41630025;0000VG17072025QA51030026;0000VG17072025QA13970027;0000VG17072025QA75370028;0000VG17072025QA72270029</t>
   </si>
   <si>
@@ -203,25 +200,28 @@
     <t>Initial</t>
   </si>
   <si>
-    <t>JV</t>
-  </si>
-  <si>
     <t>DC2380-447-4</t>
   </si>
   <si>
-    <t>60</t>
-  </si>
-  <si>
     <t>PLUS</t>
   </si>
   <si>
-    <t>SS36946587;SS10874783</t>
-  </si>
-  <si>
     <t>Pre_Allocate</t>
   </si>
   <si>
     <t>Y</t>
+  </si>
+  <si>
+    <t>VASN1707QA8130;VASN1707QA7370</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>VG</t>
+  </si>
+  <si>
+    <t>VGASN2107QA6640;VGASN2107QA4391</t>
   </si>
 </sst>
 </file>
@@ -646,7 +646,7 @@
         <v>5</v>
       </c>
       <c r="C1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D1" t="s">
         <v>4</v>
@@ -675,16 +675,16 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D2">
         <v>2</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>12</v>
@@ -693,7 +693,7 @@
         <v>16</v>
       </c>
       <c r="I2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -736,7 +736,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -857,7 +857,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -911,7 +911,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -939,7 +939,7 @@
         <v>7</v>
       </c>
       <c r="D1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -950,10 +950,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96A7137D-370A-584A-96A4-0A3597B1474D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBB7868D-AEE4-1C41-8A3F-48B060E72F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35120" yWindow="500" windowWidth="34140" windowHeight="28300" activeTab="1" xr2:uid="{42CC21F1-E411-8B4E-AF9F-23E71D9E71DE}"/>
+    <workbookView xWindow="35120" yWindow="500" windowWidth="34140" windowHeight="28300" activeTab="5" xr2:uid="{42CC21F1-E411-8B4E-AF9F-23E71D9E71DE}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateASN" sheetId="1" r:id="rId1"/>
-    <sheet name="SearchASN" sheetId="2" r:id="rId2"/>
-    <sheet name="ItemSearch" sheetId="3" r:id="rId3"/>
-    <sheet name="GoodsHolderAnnounced" sheetId="4" r:id="rId4"/>
-    <sheet name="PutawayTaskComplete" sheetId="8" r:id="rId5"/>
-    <sheet name="InboundDelivery" sheetId="10" r:id="rId6"/>
+    <sheet name="ItemSearch" sheetId="3" r:id="rId2"/>
+    <sheet name="SearchASN" sheetId="2" r:id="rId3"/>
+    <sheet name="InboundDelivery" sheetId="10" r:id="rId4"/>
+    <sheet name="GoodsHolderAnnounced" sheetId="4" r:id="rId5"/>
+    <sheet name="PutawayTaskComplete" sheetId="8" r:id="rId6"/>
     <sheet name="GoodsHolderWeighed" sheetId="5" r:id="rId7"/>
     <sheet name="InboundMaster" sheetId="6" r:id="rId8"/>
     <sheet name="BackUP" sheetId="7" r:id="rId9"/>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="43">
   <si>
     <t>Item</t>
   </si>
@@ -191,12 +191,6 @@
     <t>0000VG16072025QA71880000;0000VG16072025QA89280001</t>
   </si>
   <si>
-    <t>0000VG17072025QA76140000;0000VG17072025QA18580001;0000VG17072025QA27220002;0000VG17072025QA80720003;0000VG17072025QA27120004;0000VG17072025QA51610005;0000VG17072025QA95050006;0000VG17072025QA81350007;0000VG17072025QA60090008;0000VG17072025QA12260009;0000VG17072025QA89050010;0000VG17072025QA31840011;0000VG17072025QA66890012;0000VG17072025QA83900013;0000VG17072025QA20970014;0000VG17072025QA98670015;0000VG17072025QA75830016;0000VG17072025QA29240017;0000VG17072025QA33920018;0000VG17072025QA75940019;0000VG17072025QA36890020;0000VG17072025QA49070021;0000VG17072025QA33010022;0000VG17072025QA79000023;0000VG17072025QA78020024;0000VG17072025QA41630025;0000VG17072025QA51030026;0000VG17072025QA13970027;0000VG17072025QA75370028;0000VG17072025QA72270029</t>
-  </si>
-  <si>
-    <t>0000VG17072025QA27220002;0000VG17072025QA80720003;0000VG17072025QA27120004;0000VG17072025QA51610005;0000VG17072025QA95050006;0000VG17072025QA81350007;0000VG17072025QA60090008;0000VG17072025QA12260009;0000VG17072025QA89050010;0000VG17072025QA31840011;0000VG17072025QA66890012;0000VG17072025QA83900013;0000VG17072025QA20970014;0000VG17072025QA98670015;0000VG17072025QA75830016;0000VG17072025QA29240017;0000VG17072025QA33920018;0000VG17072025QA75940019;0000VG17072025QA36890020;0000VG17072025QA49070021;0000VG17072025QA33010022;0000VG17072025QA79000023;0000VG17072025QA78020024;0000VG17072025QA41630025;0000VG17072025QA51030026;0000VG17072025QA13970027;0000VG17072025QA75370028;0000VG17072025QA72270029</t>
-  </si>
-  <si>
     <t>Initial</t>
   </si>
   <si>
@@ -212,9 +206,6 @@
     <t>Y</t>
   </si>
   <si>
-    <t>VASN1707QA8130;VASN1707QA7370</t>
-  </si>
-  <si>
     <t>12</t>
   </si>
   <si>
@@ -222,6 +213,9 @@
   </si>
   <si>
     <t>VGASN2107QA6640;VGASN2107QA4391</t>
+  </si>
+  <si>
+    <t>0000VG21072025QA65710002;0000VG21072025QA54300003;0000VG21072025QA86650000;0000VG21072025QA25890001</t>
   </si>
 </sst>
 </file>
@@ -646,7 +640,7 @@
         <v>5</v>
       </c>
       <c r="C1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D1" t="s">
         <v>4</v>
@@ -675,16 +669,16 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D2">
         <v>2</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>12</v>
@@ -693,7 +687,7 @@
         <v>16</v>
       </c>
       <c r="I2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -708,43 +702,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33A618D3-DF17-664A-8FEB-6E7593C89614}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.1640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>1081</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B9183DE-D7AA-DE46-A3B4-9DCF4B2521A8}">
   <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -827,12 +784,50 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08F2DD08-62F1-384E-9B5D-A12F94FFD0E5}">
-  <dimension ref="A1:D7"/>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33A618D3-DF17-664A-8FEB-6E7593C89614}">
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="154.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1081</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64A059F3-6E6F-6147-A5D8-D618E64F9347}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="33.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
@@ -846,7 +841,7 @@
         <v>7</v>
       </c>
       <c r="D1" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -856,24 +851,12 @@
       <c r="B2" t="s">
         <v>6</v>
       </c>
+      <c r="C2" t="s">
+        <v>41</v>
+      </c>
       <c r="D2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="D4" s="3"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="D6" s="3"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="D7" s="3"/>
+        <v>38</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -881,6 +864,59 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08F2DD08-62F1-384E-9B5D-A12F94FFD0E5}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="104.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1081</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D3" s="3"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D4" s="3"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D6" s="3"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D7" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C28F16B0-DC10-294B-ABB9-7C124875B13D}">
   <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -911,49 +947,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64A059F3-6E6F-6147-A5D8-D618E64F9347}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="3" max="3" width="33.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.33203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>1081</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBB7868D-AEE4-1C41-8A3F-48B060E72F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F647A174-174E-D14F-B496-438596CE7714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35120" yWindow="500" windowWidth="34140" windowHeight="28300" activeTab="5" xr2:uid="{42CC21F1-E411-8B4E-AF9F-23E71D9E71DE}"/>
+    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" activeTab="6" xr2:uid="{42CC21F1-E411-8B4E-AF9F-23E71D9E71DE}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateASN" sheetId="1" r:id="rId1"/>
@@ -19,9 +19,10 @@
     <sheet name="InboundDelivery" sheetId="10" r:id="rId4"/>
     <sheet name="GoodsHolderAnnounced" sheetId="4" r:id="rId5"/>
     <sheet name="PutawayTaskComplete" sheetId="8" r:id="rId6"/>
-    <sheet name="GoodsHolderWeighed" sheetId="5" r:id="rId7"/>
-    <sheet name="InboundMaster" sheetId="6" r:id="rId8"/>
-    <sheet name="BackUP" sheetId="7" r:id="rId9"/>
+    <sheet name="ASNVerify" sheetId="11" r:id="rId7"/>
+    <sheet name="GoodsHolderWeighed" sheetId="5" r:id="rId8"/>
+    <sheet name="InboundMaster" sheetId="6" r:id="rId9"/>
+    <sheet name="BackUP" sheetId="7" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -87,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="43">
   <si>
     <t>Item</t>
   </si>
@@ -194,9 +195,6 @@
     <t>Initial</t>
   </si>
   <si>
-    <t>DC2380-447-4</t>
-  </si>
-  <si>
     <t>PLUS</t>
   </si>
   <si>
@@ -206,16 +204,19 @@
     <t>Y</t>
   </si>
   <si>
+    <t>VG</t>
+  </si>
+  <si>
     <t>12</t>
   </si>
   <si>
-    <t>VG</t>
-  </si>
-  <si>
-    <t>VGASN2107QA6640;VGASN2107QA4391</t>
-  </si>
-  <si>
-    <t>0000VG21072025QA65710002;0000VG21072025QA54300003;0000VG21072025QA86650000;0000VG21072025QA25890001</t>
+    <t>VGASN2107QA9450</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VGASN2107QA9450 </t>
+  </si>
+  <si>
+    <t>0000VG07212025QA51680000;0000VG07212025QA81720001</t>
   </si>
 </sst>
 </file>
@@ -266,7 +267,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -274,17 +275,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -669,25 +686,25 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -697,6 +714,132 @@
       <c r="H4" s="4"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" display="924156-100-S@DN0560-885-6;DD9293-100-7" xr:uid="{E0C922B7-1BF3-2A4D-8EC6-6E10A57A0112}"/>
+    <hyperlink ref="F2" r:id="rId2" display="12@12;12" xr:uid="{37612C0C-F9F1-7C48-819D-42E96C06239D}"/>
+    <hyperlink ref="G2" r:id="rId3" display="6@6;6" xr:uid="{4267A627-AAEB-B240-8534-5B72B1FAE026}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{594297BC-D256-A64D-9D4F-D6CE762B919E}">
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="38.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1">
+        <v>1081</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1081</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1081</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>1081</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F1" r:id="rId1" display="6@6;6" xr:uid="{18FB1008-07E0-5C46-8F7F-496B13292E2B}"/>
+    <hyperlink ref="E1" r:id="rId2" display="6@6;6" xr:uid="{06896637-CD23-B347-9B8A-8AE6C644740F}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -841,7 +984,7 @@
         <v>7</v>
       </c>
       <c r="D1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -852,10 +995,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -956,6 +1099,41 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A9C540C-E4DB-1D41-B406-C8AFADE06F3D}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="34.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="5">
+        <v>1081</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A3C3BB5-2CD4-434E-8D5E-3EF32DB5E8EC}">
   <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -996,7 +1174,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAD0A41D-4930-B447-B269-74D79A2958B3}">
   <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1031,125 +1209,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{594297BC-D256-A64D-9D4F-D6CE762B919E}">
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="4" max="4" width="38.1640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1">
-        <v>1081</v>
-      </c>
-      <c r="B1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>1081</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>1081</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>1081</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="F1" r:id="rId1" display="6@6;6" xr:uid="{18FB1008-07E0-5C46-8F7F-496B13292E2B}"/>
-    <hyperlink ref="E1" r:id="rId2" display="6@6;6" xr:uid="{06896637-CD23-B347-9B8A-8AE6C644740F}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F647A174-174E-D14F-B496-438596CE7714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8A1F2FA-4661-2E41-9D04-AC2B091182CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" activeTab="6" xr2:uid="{42CC21F1-E411-8B4E-AF9F-23E71D9E71DE}"/>
+    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" activeTab="4" xr2:uid="{42CC21F1-E411-8B4E-AF9F-23E71D9E71DE}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateASN" sheetId="1" r:id="rId1"/>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="43">
   <si>
     <t>Item</t>
   </si>
@@ -1176,7 +1176,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAD0A41D-4930-B447-B269-74D79A2958B3}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" bestFit="1" customWidth="1"/>
@@ -1206,6 +1206,11 @@
         <v>26</v>
       </c>
     </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F2" t="s">
+        <v>37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8A1F2FA-4661-2E41-9D04-AC2B091182CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAD3B945-34D7-6246-9AB8-3C0E069845C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" activeTab="4" xr2:uid="{42CC21F1-E411-8B4E-AF9F-23E71D9E71DE}"/>
   </bookViews>
@@ -210,13 +210,13 @@
     <t>12</t>
   </si>
   <si>
-    <t>VGASN2107QA9450</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VGASN2107QA9450 </t>
-  </si>
-  <si>
-    <t>0000VG07212025QA51680000;0000VG07212025QA81720001</t>
+    <t>0000VG07222025QA35600000;0000VG07222025QA23240001;0000VG07222025QA27740002;0000VG07222025QA57710003</t>
+  </si>
+  <si>
+    <t>VGASN2207QA8260;VGASN2207QA5061</t>
+  </si>
+  <si>
+    <t>VGASN0722QA6520;VGASN0722QA4571</t>
   </si>
 </sst>
 </file>
@@ -689,7 +689,7 @@
         <v>38</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>32</v>
@@ -956,7 +956,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -995,7 +995,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D2" t="s">
         <v>37</v>
@@ -1011,6 +1011,7 @@
   <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="104.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1035,7 +1036,7 @@
       <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C2" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1090,7 +1091,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAD3B945-34D7-6246-9AB8-3C0E069845C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B185791B-2640-BF42-928A-AE062BCB54D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" activeTab="4" xr2:uid="{42CC21F1-E411-8B4E-AF9F-23E71D9E71DE}"/>
+    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" activeTab="5" xr2:uid="{42CC21F1-E411-8B4E-AF9F-23E71D9E71DE}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateASN" sheetId="1" r:id="rId1"/>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="43">
   <si>
     <t>Item</t>
   </si>
@@ -210,13 +210,13 @@
     <t>12</t>
   </si>
   <si>
-    <t>0000VG07222025QA35600000;0000VG07222025QA23240001;0000VG07222025QA27740002;0000VG07222025QA57710003</t>
-  </si>
-  <si>
     <t>VGASN2207QA8260;VGASN2207QA5061</t>
   </si>
   <si>
     <t>VGASN0722QA6520;VGASN0722QA4571</t>
+  </si>
+  <si>
+    <t>Failed</t>
   </si>
 </sst>
 </file>
@@ -956,7 +956,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -995,7 +995,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
         <v>37</v>
@@ -1037,7 +1037,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -1062,14 +1062,14 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C28F16B0-DC10-294B-ABB9-7C124875B13D}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="47.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -1082,16 +1082,22 @@
       <c r="D1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1081</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
-        <v>40</v>
+      <c r="C2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1126,7 +1132,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B185791B-2640-BF42-928A-AE062BCB54D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6753AB9-E9EB-D346-9A2F-2D1A6CE42C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" activeTab="5" xr2:uid="{42CC21F1-E411-8B4E-AF9F-23E71D9E71DE}"/>
+    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" activeTab="7" xr2:uid="{42CC21F1-E411-8B4E-AF9F-23E71D9E71DE}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateASN" sheetId="1" r:id="rId1"/>
@@ -18,9 +18,9 @@
     <sheet name="SearchASN" sheetId="2" r:id="rId3"/>
     <sheet name="InboundDelivery" sheetId="10" r:id="rId4"/>
     <sheet name="GoodsHolderAnnounced" sheetId="4" r:id="rId5"/>
-    <sheet name="PutawayTaskComplete" sheetId="8" r:id="rId6"/>
-    <sheet name="ASNVerify" sheetId="11" r:id="rId7"/>
-    <sheet name="GoodsHolderWeighed" sheetId="5" r:id="rId8"/>
+    <sheet name="GoodsHolderWeighed" sheetId="5" r:id="rId6"/>
+    <sheet name="PutawayTaskComplete" sheetId="8" r:id="rId7"/>
+    <sheet name="ASNVerify" sheetId="11" r:id="rId8"/>
     <sheet name="InboundMaster" sheetId="6" r:id="rId9"/>
     <sheet name="BackUP" sheetId="7" r:id="rId10"/>
   </sheets>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="43">
   <si>
     <t>Item</t>
   </si>
@@ -189,9 +189,6 @@
     <t>DD9293-100-7</t>
   </si>
   <si>
-    <t>0000VG16072025QA71880000;0000VG16072025QA89280001</t>
-  </si>
-  <si>
     <t>Initial</t>
   </si>
   <si>
@@ -210,13 +207,16 @@
     <t>12</t>
   </si>
   <si>
-    <t>VGASN2207QA8260;VGASN2207QA5061</t>
-  </si>
-  <si>
     <t>VGASN0722QA6520;VGASN0722QA4571</t>
   </si>
   <si>
     <t>Failed</t>
+  </si>
+  <si>
+    <t>Cancelled</t>
+  </si>
+  <si>
+    <t>VGASN0723QA1350</t>
   </si>
 </sst>
 </file>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="C1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D1" t="s">
         <v>4</v>
@@ -686,7 +686,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2">
         <v>2</v>
@@ -695,7 +695,7 @@
         <v>32</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>12</v>
@@ -704,7 +704,7 @@
         <v>16</v>
       </c>
       <c r="I2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -956,7 +956,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -984,7 +984,7 @@
         <v>7</v>
       </c>
       <c r="D1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -995,10 +995,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1037,7 +1037,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -1061,15 +1061,56 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A3C3BB5-2CD4-434E-8D5E-3EF32DB5E8EC}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="52.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1081</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C28F16B0-DC10-294B-ABB9-7C124875B13D}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="34.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="47.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -1083,21 +1124,24 @@
         <v>13</v>
       </c>
       <c r="E1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1081</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>1081</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E2" t="s">
-        <v>37</v>
+      <c r="F2" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1105,7 +1149,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A9C540C-E4DB-1D41-B406-C8AFADE06F3D}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1132,48 +1176,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A3C3BB5-2CD4-434E-8D5E-3EF32DB5E8EC}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.1640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>1081</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1215,7 +1218,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="F2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6753AB9-E9EB-D346-9A2F-2D1A6CE42C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2327109D-7FBA-124C-A016-6077C4E4297E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" activeTab="7" xr2:uid="{42CC21F1-E411-8B4E-AF9F-23E71D9E71DE}"/>
+    <workbookView xWindow="12220" yWindow="2880" windowWidth="49400" windowHeight="28300" xr2:uid="{42CC21F1-E411-8B4E-AF9F-23E71D9E71DE}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateASN" sheetId="1" r:id="rId1"/>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="43">
   <si>
     <t>Item</t>
   </si>
@@ -204,19 +204,19 @@
     <t>VG</t>
   </si>
   <si>
+    <t>VGASN0722QA6520;VGASN0722QA4571</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
+    <t>Cancelled</t>
+  </si>
+  <si>
+    <t>VGASN0723QA1350</t>
+  </si>
+  <si>
     <t>12</t>
-  </si>
-  <si>
-    <t>VGASN0722QA6520;VGASN0722QA4571</t>
-  </si>
-  <si>
-    <t>Failed</t>
-  </si>
-  <si>
-    <t>Cancelled</t>
-  </si>
-  <si>
-    <t>VGASN0723QA1350</t>
   </si>
 </sst>
 </file>
@@ -637,7 +637,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAFEB96B-A165-0D40-BEA2-4B797ACC428A}">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
@@ -695,7 +695,7 @@
         <v>32</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>12</v>
@@ -709,9 +709,6 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="H3" s="4"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="H4" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -956,7 +953,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -995,7 +992,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
         <v>36</v>
@@ -1037,7 +1034,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -1093,7 +1090,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1124,10 +1121,10 @@
         <v>13</v>
       </c>
       <c r="E1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" t="s">
         <v>40</v>
-      </c>
-      <c r="F1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -1138,7 +1135,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F2" t="s">
         <v>36</v>
@@ -1176,7 +1173,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1217,6 +1214,21 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" t="s">
+        <v>36</v>
+      </c>
       <c r="F2" t="s">
         <v>36</v>
       </c>

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2327109D-7FBA-124C-A016-6077C4E4297E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C269EE28-6158-3840-8195-4CB750AB0B57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12220" yWindow="2880" windowWidth="49400" windowHeight="28300" xr2:uid="{42CC21F1-E411-8B4E-AF9F-23E71D9E71DE}"/>
+    <workbookView xWindow="60720" yWindow="3900" windowWidth="49400" windowHeight="28300" activeTab="8" xr2:uid="{42CC21F1-E411-8B4E-AF9F-23E71D9E71DE}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateASN" sheetId="1" r:id="rId1"/>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="43">
   <si>
     <t>Item</t>
   </si>
@@ -1220,18 +1220,6 @@
       <c r="B2" t="s">
         <v>36</v>
       </c>
-      <c r="C2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F2" t="s">
-        <v>36</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C269EE28-6158-3840-8195-4CB750AB0B57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{223A1C50-654B-1046-A588-265AC75A2B76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60720" yWindow="3900" windowWidth="49400" windowHeight="28300" activeTab="8" xr2:uid="{42CC21F1-E411-8B4E-AF9F-23E71D9E71DE}"/>
+    <workbookView xWindow="37800" yWindow="500" windowWidth="49400" windowHeight="28300" xr2:uid="{42CC21F1-E411-8B4E-AF9F-23E71D9E71DE}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateASN" sheetId="1" r:id="rId1"/>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="42">
   <si>
     <t>Item</t>
   </si>
@@ -214,9 +214,6 @@
   </si>
   <si>
     <t>VGASN0723QA1350</t>
-  </si>
-  <si>
-    <t>12</t>
   </si>
 </sst>
 </file>
@@ -691,14 +688,14 @@
       <c r="D2">
         <v>2</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>32</v>
+      <c r="E2" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>16</v>
@@ -712,9 +709,8 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" display="924156-100-S@DN0560-885-6;DD9293-100-7" xr:uid="{E0C922B7-1BF3-2A4D-8EC6-6E10A57A0112}"/>
-    <hyperlink ref="F2" r:id="rId2" display="12@12;12" xr:uid="{37612C0C-F9F1-7C48-819D-42E96C06239D}"/>
-    <hyperlink ref="G2" r:id="rId3" display="6@6;6" xr:uid="{4267A627-AAEB-B240-8534-5B72B1FAE026}"/>
+    <hyperlink ref="G2" r:id="rId1" display="6@6;6" xr:uid="{F1DA680C-31E4-B04D-BF6C-393396D2D0DF}"/>
+    <hyperlink ref="F2" r:id="rId2" display="6@6;6" xr:uid="{E4D57CD7-9BA4-B040-ABE9-91A7D327297F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1214,10 +1210,7 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="F2" t="s">
         <v>36</v>
       </c>
     </row>

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{223A1C50-654B-1046-A588-265AC75A2B76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29E76241-1260-0549-A248-DC1073E11C9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="37800" yWindow="500" windowWidth="49400" windowHeight="28300" xr2:uid="{42CC21F1-E411-8B4E-AF9F-23E71D9E71DE}"/>
+    <workbookView xWindow="37800" yWindow="500" windowWidth="49400" windowHeight="28300" activeTab="8" xr2:uid="{42CC21F1-E411-8B4E-AF9F-23E71D9E71DE}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateASN" sheetId="1" r:id="rId1"/>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="43">
   <si>
     <t>Item</t>
   </si>
@@ -214,6 +214,9 @@
   </si>
   <si>
     <t>VGASN0723QA1350</t>
+  </si>
+  <si>
+    <t>12</t>
   </si>
 </sst>
 </file>
@@ -689,13 +692,13 @@
         <v>2</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>16</v>
@@ -1210,7 +1213,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="F2" t="s">
+      <c r="A2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" t="s">
         <v>36</v>
       </c>
     </row>

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29E76241-1260-0549-A248-DC1073E11C9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F03B8B9-9F3C-9F47-9C34-1C94DF989BFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="37800" yWindow="500" windowWidth="49400" windowHeight="28300" activeTab="8" xr2:uid="{42CC21F1-E411-8B4E-AF9F-23E71D9E71DE}"/>
+    <workbookView xWindow="48100" yWindow="4080" windowWidth="36000" windowHeight="22500" xr2:uid="{42CC21F1-E411-8B4E-AF9F-23E71D9E71DE}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateASN" sheetId="1" r:id="rId1"/>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="45">
   <si>
     <t>Item</t>
   </si>
@@ -192,9 +192,6 @@
     <t>Initial</t>
   </si>
   <si>
-    <t>PLUS</t>
-  </si>
-  <si>
     <t>Pre_Allocate</t>
   </si>
   <si>
@@ -216,7 +213,16 @@
     <t>VGASN0723QA1350</t>
   </si>
   <si>
-    <t>12</t>
+    <t>DEV</t>
+  </si>
+  <si>
+    <t>924156-100-S@420420-420-M;DD9293-100-7</t>
+  </si>
+  <si>
+    <t>12@12;12</t>
+  </si>
+  <si>
+    <t>6@6;6</t>
   </si>
 </sst>
 </file>
@@ -637,7 +643,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAFEB96B-A165-0D40-BEA2-4B797ACC428A}">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
@@ -686,42 +692,35 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="F2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="H3" s="4"/>
+        <v>18</v>
+      </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" display="6@6;6" xr:uid="{F1DA680C-31E4-B04D-BF6C-393396D2D0DF}"/>
-    <hyperlink ref="F2" r:id="rId2" display="6@6;6" xr:uid="{E4D57CD7-9BA4-B040-ABE9-91A7D327297F}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{594297BC-D256-A64D-9D4F-D6CE762B919E}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="38.1640625" bestFit="1" customWidth="1"/>
@@ -831,10 +830,39 @@
         <v>18</v>
       </c>
     </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>1081</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" t="s">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="F1" r:id="rId1" display="6@6;6" xr:uid="{18FB1008-07E0-5C46-8F7F-496B13292E2B}"/>
     <hyperlink ref="E1" r:id="rId2" display="6@6;6" xr:uid="{06896637-CD23-B347-9B8A-8AE6C644740F}"/>
+    <hyperlink ref="F5" r:id="rId3" xr:uid="{71E6558D-0897-F140-9604-ACCB58EB156F}"/>
+    <hyperlink ref="E5" r:id="rId4" xr:uid="{AA51A693-BC84-C543-8465-6F5E827C2100}"/>
+    <hyperlink ref="D5" r:id="rId5" xr:uid="{ACA04CD8-879F-B941-8456-D9C41F479230}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -877,7 +905,7 @@
         <v>1081</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="C2">
         <v>3</v>
@@ -891,7 +919,7 @@
         <v>1081</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -905,7 +933,7 @@
         <v>1081</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -952,7 +980,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -980,7 +1008,7 @@
         <v>7</v>
       </c>
       <c r="D1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -991,10 +1019,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1033,7 +1061,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -1089,7 +1117,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1120,10 +1148,10 @@
         <v>13</v>
       </c>
       <c r="E1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1" t="s">
         <v>39</v>
-      </c>
-      <c r="F1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -1134,10 +1162,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1172,7 +1200,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1213,11 +1241,8 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B2" t="s">
-        <v>36</v>
+      <c r="F2" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F03B8B9-9F3C-9F47-9C34-1C94DF989BFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{853D73C9-27DC-F043-AAA4-D8D9E00E0ADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="48100" yWindow="4080" windowWidth="36000" windowHeight="22500" xr2:uid="{42CC21F1-E411-8B4E-AF9F-23E71D9E71DE}"/>
+    <workbookView xWindow="37420" yWindow="5560" windowWidth="36000" windowHeight="22500" activeTab="8" xr2:uid="{42CC21F1-E411-8B4E-AF9F-23E71D9E71DE}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateASN" sheetId="1" r:id="rId1"/>
@@ -695,16 +695,16 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>12</v>
+        <v>2</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>16</v>
@@ -714,6 +714,11 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{C768F6CF-9352-5447-AC8E-77834F7531F4}"/>
+    <hyperlink ref="F2" r:id="rId2" xr:uid="{07493ED9-AB47-FB44-BDD2-E84A454127C8}"/>
+    <hyperlink ref="E2" r:id="rId3" xr:uid="{E0AA5A6A-22F7-5440-AFDB-A9ACBB169FCC}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{853D73C9-27DC-F043-AAA4-D8D9E00E0ADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1FF23EA-D7F7-1547-AE15-838570A6E234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="37420" yWindow="5560" windowWidth="36000" windowHeight="22500" activeTab="8" xr2:uid="{42CC21F1-E411-8B4E-AF9F-23E71D9E71DE}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="8" xr2:uid="{42CC21F1-E411-8B4E-AF9F-23E71D9E71DE}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateASN" sheetId="1" r:id="rId1"/>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="45">
   <si>
     <t>Item</t>
   </si>
@@ -198,9 +198,6 @@
     <t>Y</t>
   </si>
   <si>
-    <t>VG</t>
-  </si>
-  <si>
     <t>VGASN0722QA6520;VGASN0722QA4571</t>
   </si>
   <si>
@@ -213,9 +210,6 @@
     <t>VGASN0723QA1350</t>
   </si>
   <si>
-    <t>DEV</t>
-  </si>
-  <si>
     <t>924156-100-S@420420-420-M;DD9293-100-7</t>
   </si>
   <si>
@@ -223,6 +217,12 @@
   </si>
   <si>
     <t>6@6;6</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>112308-011-XL</t>
   </si>
 </sst>
 </file>
@@ -691,20 +691,20 @@
       <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
-        <v>36</v>
+      <c r="C2">
+        <v>81</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>43</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>16</v>
@@ -715,9 +715,9 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" xr:uid="{C768F6CF-9352-5447-AC8E-77834F7531F4}"/>
-    <hyperlink ref="F2" r:id="rId2" xr:uid="{07493ED9-AB47-FB44-BDD2-E84A454127C8}"/>
-    <hyperlink ref="E2" r:id="rId3" xr:uid="{E0AA5A6A-22F7-5440-AFDB-A9ACBB169FCC}"/>
+    <hyperlink ref="G2" r:id="rId1" display="6@6;6" xr:uid="{C768F6CF-9352-5447-AC8E-77834F7531F4}"/>
+    <hyperlink ref="F2" r:id="rId2" display="12@12;12" xr:uid="{07493ED9-AB47-FB44-BDD2-E84A454127C8}"/>
+    <hyperlink ref="E2" r:id="rId3" display="924156-100-S@420420-420-M;DD9293-100-7" xr:uid="{E0AA5A6A-22F7-5440-AFDB-A9ACBB169FCC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -846,13 +846,13 @@
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>16</v>
@@ -910,7 +910,7 @@
         <v>1081</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="C2">
         <v>3</v>
@@ -924,7 +924,7 @@
         <v>1081</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -938,7 +938,7 @@
         <v>1081</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -985,7 +985,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1024,7 +1024,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
         <v>35</v>
@@ -1066,7 +1066,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -1122,7 +1122,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1153,10 +1153,10 @@
         <v>13</v>
       </c>
       <c r="E1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" t="s">
         <v>38</v>
-      </c>
-      <c r="F1" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -1167,7 +1167,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F2" t="s">
         <v>35</v>
@@ -1205,7 +1205,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1FF23EA-D7F7-1547-AE15-838570A6E234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{732F1528-91C7-D349-8095-56C6C49D2845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="8" xr2:uid="{42CC21F1-E411-8B4E-AF9F-23E71D9E71DE}"/>
+    <workbookView xWindow="51080" yWindow="6000" windowWidth="30240" windowHeight="18880" xr2:uid="{42CC21F1-E411-8B4E-AF9F-23E71D9E71DE}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateASN" sheetId="1" r:id="rId1"/>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="43">
   <si>
     <t>Item</t>
   </si>
@@ -217,12 +217,6 @@
   </si>
   <si>
     <t>6@6;6</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>112308-011-XL</t>
   </si>
 </sst>
 </file>
@@ -698,13 +692,13 @@
         <v>1</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>16</v>
@@ -715,9 +709,9 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" display="6@6;6" xr:uid="{C768F6CF-9352-5447-AC8E-77834F7531F4}"/>
-    <hyperlink ref="F2" r:id="rId2" display="12@12;12" xr:uid="{07493ED9-AB47-FB44-BDD2-E84A454127C8}"/>
-    <hyperlink ref="E2" r:id="rId3" display="924156-100-S@420420-420-M;DD9293-100-7" xr:uid="{E0AA5A6A-22F7-5440-AFDB-A9ACBB169FCC}"/>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{F3B2D7A0-D48E-9E43-8044-718E6F0B870E}"/>
+    <hyperlink ref="F2" r:id="rId2" xr:uid="{FCC41D0C-7137-EF43-A445-4AB7F4DECBF0}"/>
+    <hyperlink ref="E2" r:id="rId3" xr:uid="{E80A8163-3349-2D45-90C3-56D0EC02514F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{732F1528-91C7-D349-8095-56C6C49D2845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64B7EC2A-A369-5842-BDE7-21BC6B981A22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51080" yWindow="6000" windowWidth="30240" windowHeight="18880" xr2:uid="{42CC21F1-E411-8B4E-AF9F-23E71D9E71DE}"/>
+    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" activeTab="9" xr2:uid="{42CC21F1-E411-8B4E-AF9F-23E71D9E71DE}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateASN" sheetId="1" r:id="rId1"/>
@@ -21,8 +21,9 @@
     <sheet name="GoodsHolderWeighed" sheetId="5" r:id="rId6"/>
     <sheet name="PutawayTaskComplete" sheetId="8" r:id="rId7"/>
     <sheet name="ASNVerify" sheetId="11" r:id="rId8"/>
-    <sheet name="InboundMaster" sheetId="6" r:id="rId9"/>
-    <sheet name="BackUP" sheetId="7" r:id="rId10"/>
+    <sheet name="MHEJournal" sheetId="12" r:id="rId9"/>
+    <sheet name="InboundMaster" sheetId="6" r:id="rId10"/>
+    <sheet name="BackUP" sheetId="7" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -88,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="47">
   <si>
     <t>Item</t>
   </si>
@@ -217,6 +218,18 @@
   </si>
   <si>
     <t>6@6;6</t>
+  </si>
+  <si>
+    <t>Message Type</t>
+  </si>
+  <si>
+    <t>PutawayTaskResult</t>
+  </si>
+  <si>
+    <t>VG</t>
+  </si>
+  <si>
+    <t>VGASN0804QA2820</t>
   </si>
 </sst>
 </file>
@@ -685,20 +698,20 @@
       <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2">
-        <v>81</v>
+      <c r="C2" t="s">
+        <v>45</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>42</v>
+      <c r="E2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>16</v>
@@ -708,16 +721,62 @@
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" xr:uid="{F3B2D7A0-D48E-9E43-8044-718E6F0B870E}"/>
-    <hyperlink ref="F2" r:id="rId2" xr:uid="{FCC41D0C-7137-EF43-A445-4AB7F4DECBF0}"/>
-    <hyperlink ref="E2" r:id="rId3" xr:uid="{E80A8163-3349-2D45-90C3-56D0EC02514F}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAD0A41D-4930-B447-B269-74D79A2958B3}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{594297BC-D256-A64D-9D4F-D6CE762B919E}">
   <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1208,40 +1267,46 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAD0A41D-4930-B447-B269-74D79A2958B3}">
-  <dimension ref="A1:F2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB2CDCA8-B1C4-F24C-B483-23BE01BED78D}">
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="C1" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D1" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="F2" t="s">
-        <v>35</v>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1081</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64B7EC2A-A369-5842-BDE7-21BC6B981A22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28C0A5C4-387C-9D4D-AC22-AD4C13FF1C50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" activeTab="9" xr2:uid="{42CC21F1-E411-8B4E-AF9F-23E71D9E71DE}"/>
   </bookViews>
@@ -89,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="47">
   <si>
     <t>Item</t>
   </si>
@@ -758,15 +758,6 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C2" t="s">
-        <v>35</v>
-      </c>
       <c r="F2" t="s">
         <v>35</v>
       </c>

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF4AA6C2-F0C5-DC4F-982B-434AD25F7809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BA20803-EDA6-D14D-A812-310882F84DC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E5361F4-965F-2343-AD6B-EB598FED26A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{400AC945-C570-F148-AA80-91A482DF7FDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateASN" sheetId="1" r:id="rId1"/>
-    <sheet name="MasterInput" sheetId="2" r:id="rId2"/>
-    <sheet name="InboundMaster" sheetId="3" r:id="rId3"/>
+    <sheet name="InboundMaster" sheetId="2" r:id="rId2"/>
+    <sheet name="MasterInput" sheetId="3" r:id="rId3"/>
     <sheet name="ItemSearch" sheetId="4" r:id="rId4"/>
     <sheet name="SearchASN" sheetId="5" r:id="rId5"/>
     <sheet name="BackUP" sheetId="6" r:id="rId6"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="47">
   <si>
     <t>Plant</t>
   </si>
@@ -88,6 +88,9 @@
     <t>924156-100-S</t>
   </si>
   <si>
+    <t>24</t>
+  </si>
+  <si>
     <t>6</t>
   </si>
   <si>
@@ -97,6 +100,30 @@
     <t>AUPU</t>
   </si>
   <si>
+    <t>CreateASN</t>
+  </si>
+  <si>
+    <t>InboundDelivery</t>
+  </si>
+  <si>
+    <t>GHAnnounced</t>
+  </si>
+  <si>
+    <t>GHWeighed</t>
+  </si>
+  <si>
+    <t>PutawayComplete</t>
+  </si>
+  <si>
+    <t>ASNVerify</t>
+  </si>
+  <si>
+    <t>RunAll</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
     <t>ASNID</t>
   </si>
   <si>
@@ -112,39 +139,9 @@
     <t>1081</t>
   </si>
   <si>
-    <t>VGASN0806QA5260</t>
-  </si>
-  <si>
-    <t>00V08062025QA3890</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
     <t>N</t>
   </si>
   <si>
-    <t>CreateASN</t>
-  </si>
-  <si>
-    <t>InboundDelivery</t>
-  </si>
-  <si>
-    <t>GHAnnounced</t>
-  </si>
-  <si>
-    <t>GHWeighed</t>
-  </si>
-  <si>
-    <t>PutawayComplete</t>
-  </si>
-  <si>
-    <t>ASNVerify</t>
-  </si>
-  <si>
-    <t>RunAll</t>
-  </si>
-  <si>
     <t>Num_of_Items_to_search</t>
   </si>
   <si>
@@ -166,6 +163,9 @@
     <t>Footwear</t>
   </si>
   <si>
+    <t>VGASN0807QA1250</t>
+  </si>
+  <si>
     <t>924156-100-S;420420-420-M;DD9293-100-7</t>
   </si>
   <si>
@@ -190,7 +190,7 @@
     <t>6@6;6</t>
   </si>
   <si>
-    <t>VGASN0807QA1250</t>
+    <t xml:space="preserve">VGASN0807QA6190 </t>
   </si>
 </sst>
 </file>
@@ -659,13 +659,13 @@
         <v>12</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -675,56 +675,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
-  <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
@@ -738,40 +688,89 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="74" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -795,16 +794,16 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" t="s">
         <v>31</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>32</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>33</v>
-      </c>
-      <c r="F1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -818,7 +817,7 @@
         <v>3</v>
       </c>
       <c r="E2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -832,7 +831,7 @@
         <v>3</v>
       </c>
       <c r="E3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -846,7 +845,7 @@
         <v>3</v>
       </c>
       <c r="E4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -876,7 +875,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -887,7 +886,7 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -923,10 +922,10 @@
         <v>39</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -949,10 +948,10 @@
         <v>41</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -969,16 +968,16 @@
         <v>11</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -995,16 +994,16 @@
         <v>42</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1027,10 +1026,10 @@
         <v>45</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="51200" yWindow="2400" windowWidth="36000" windowHeight="22500" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CreateASN" sheetId="1" state="visible" r:id="rId1"/>
@@ -596,7 +596,7 @@
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
@@ -680,16 +680,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -750,12 +740,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0807QA6470</t>
+          <t>VGASN0807QA9430</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V08072025QA8540;00V08072025QA3031;00V08072025QA8512;00V08072025QA7163</t>
+          <t>00V08072025QA8490;00V08072025QA1571</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A365858-AF2C-8D49-8561-D7B8A7166DE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74E68197-1412-AA46-A6E5-05149FE4CB68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="70120" yWindow="2260" windowWidth="36000" windowHeight="22500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="66400" yWindow="2260" windowWidth="36000" windowHeight="22500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateASN" sheetId="1" r:id="rId1"/>
     <sheet name="InboundMaster" sheetId="2" r:id="rId2"/>
     <sheet name="MasterInput" sheetId="3" r:id="rId3"/>
-    <sheet name="ItemSearch" sheetId="4" r:id="rId4"/>
-    <sheet name="SearchASN" sheetId="5" r:id="rId5"/>
-    <sheet name="BackUP" sheetId="6" r:id="rId6"/>
+    <sheet name="ExceptionInput" sheetId="7" r:id="rId4"/>
+    <sheet name="ItemSearch" sheetId="4" r:id="rId5"/>
+    <sheet name="SearchASN" sheetId="5" r:id="rId6"/>
+    <sheet name="BackUP" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -50,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="48">
   <si>
     <t>Plant</t>
   </si>
@@ -88,9 +89,6 @@
     <t>924156-365-M;924157-417-2XL;924156-836-XL</t>
   </si>
   <si>
-    <t>12;12;12</t>
-  </si>
-  <si>
     <t>6;6;6</t>
   </si>
   <si>
@@ -139,19 +137,13 @@
     <t>1081</t>
   </si>
   <si>
-    <t>VGASN0821QA4940</t>
-  </si>
-  <si>
-    <t>00V08212025QA6060;00V08212025QA9731;00V08212025QA1212;00V08212025QA2993;00V08212025QA6144;00V08212025QA6275</t>
+    <t>VGASN0822QA3290</t>
+  </si>
+  <si>
+    <t>00V08222025QA27300;00V08222025QA17401;00V08222025QA54002</t>
   </si>
   <si>
     <t>N</t>
-  </si>
-  <si>
-    <t>VGASN0821QA4851</t>
-  </si>
-  <si>
-    <t>00V08212025QA6066;00V08212025QA6877;00V08212025QA6078;00V08212025QA3019;00V08212025QA31110;00V08212025QA27511</t>
   </si>
   <si>
     <t>Num_of_Items_to_search</t>
@@ -662,7 +654,7 @@
         <v>10</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>11</v>
@@ -671,13 +663,13 @@
         <v>12</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" t="s">
         <v>14</v>
-      </c>
-      <c r="I2" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -700,30 +692,30 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>19</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>20</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>21</v>
-      </c>
-      <c r="G1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="C2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -733,11 +725,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
-    <col min="4" max="4" width="112.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="58.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -748,56 +744,36 @@
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
       </c>
       <c r="C2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" t="s">
         <v>29</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" t="s">
         <v>30</v>
-      </c>
-      <c r="E2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -806,6 +782,50 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9C0EB67-F535-4248-A96A-EF5AEC1DD233}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="58.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -825,16 +845,16 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" t="s">
         <v>34</v>
-      </c>
-      <c r="D1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -848,10 +868,10 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -865,10 +885,10 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -882,10 +902,10 @@
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -897,7 +917,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -915,7 +935,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -926,7 +946,7 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -934,7 +954,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -953,19 +973,19 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" t="s">
         <v>14</v>
-      </c>
-      <c r="H1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -979,19 +999,19 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
         <v>14</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1005,19 +1025,19 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" t="s">
         <v>14</v>
-      </c>
-      <c r="H3" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1031,19 +1051,19 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" t="s">
         <v>14</v>
-      </c>
-      <c r="H4" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1057,19 +1077,19 @@
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" t="s">
         <v>14</v>
-      </c>
-      <c r="H5" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52E68214-6472-6B4D-8018-E9DD01B7BD2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACF96D98-FA1F-C349-BCC8-CCBDB400972B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="49">
   <si>
     <t>Plant</t>
   </si>
@@ -149,9 +149,6 @@
     <t>DiversionCodeId</t>
   </si>
   <si>
-    <t>STORAGE</t>
-  </si>
-  <si>
     <t>Num_of_Items_to_search</t>
   </si>
   <si>
@@ -198,6 +195,9 @@
   </si>
   <si>
     <t>6@6;6</t>
+  </si>
+  <si>
+    <t>FirstSKU</t>
   </si>
 </sst>
 </file>
@@ -801,27 +801,35 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
-  <cols>
-    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:4">
       <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
-        <v>32</v>
+      <c r="D2" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -849,16 +857,16 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" t="s">
         <v>33</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>34</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>35</v>
-      </c>
-      <c r="F1" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -872,7 +880,7 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F2" t="s">
         <v>22</v>
@@ -889,7 +897,7 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F3" t="s">
         <v>22</v>
@@ -906,7 +914,7 @@
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F4" t="s">
         <v>22</v>
@@ -950,7 +958,7 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -977,13 +985,13 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="F1" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>13</v>
@@ -1003,13 +1011,13 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="F2" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>13</v>
@@ -1055,7 +1063,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>12</v>
@@ -1081,13 +1089,13 @@
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>13</v>

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACF96D98-FA1F-C349-BCC8-CCBDB400972B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D957E2-9F7A-F24D-BC6F-9B4F6A3C32DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateASN" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="50">
   <si>
     <t>Plant</t>
   </si>
@@ -198,6 +198,9 @@
   </si>
   <si>
     <t>FirstSKU</t>
+  </si>
+  <si>
+    <t>924156-365-M</t>
   </si>
 </sst>
 </file>
@@ -683,7 +686,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>12</v>
@@ -740,7 +743,10 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="G2" t="s">
+      <c r="A2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" t="s">
         <v>22</v>
       </c>
     </row>

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D957E2-9F7A-F24D-BC6F-9B4F6A3C32DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A87EF23-08C6-1F42-9B7B-88AC9E5CD9B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="59440" yWindow="4060" windowWidth="36000" windowHeight="22500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateASN" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="50">
   <si>
     <t>Plant</t>
   </si>
@@ -86,105 +86,111 @@
     <t>VG</t>
   </si>
   <si>
+    <t>924156-365-S</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>0005005401</t>
+  </si>
+  <si>
+    <t>AUPU</t>
+  </si>
+  <si>
+    <t>CreateASN</t>
+  </si>
+  <si>
+    <t>InboundDelivery</t>
+  </si>
+  <si>
+    <t>GHAnnounced</t>
+  </si>
+  <si>
+    <t>GHWeighed</t>
+  </si>
+  <si>
+    <t>PutawayComplete</t>
+  </si>
+  <si>
+    <t>ASNVerify</t>
+  </si>
+  <si>
+    <t>RunAll</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>ASNID</t>
+  </si>
+  <si>
+    <t>LPNID</t>
+  </si>
+  <si>
+    <t>Pre_Allocate</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
+    <t>1081</t>
+  </si>
+  <si>
+    <t>VGASN0825QA8410</t>
+  </si>
+  <si>
+    <t>00V08252025QA11000</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>DiversionCodeId</t>
+  </si>
+  <si>
+    <t>FIRST_SKU</t>
+  </si>
+  <si>
+    <t>Num_of_Items_to_search</t>
+  </si>
+  <si>
+    <t>Search_by_Item</t>
+  </si>
+  <si>
+    <t>Search_by_Product_Type</t>
+  </si>
+  <si>
+    <t>Search_by_Missing_Dims</t>
+  </si>
+  <si>
+    <t>Apparel</t>
+  </si>
+  <si>
+    <t>Equipment</t>
+  </si>
+  <si>
+    <t>Footwear</t>
+  </si>
+  <si>
+    <t>VGASN0824QA1080</t>
+  </si>
+  <si>
+    <t>924156-100-S;420420-420-M;DD9293-100-7</t>
+  </si>
+  <si>
+    <t>6;6;6</t>
+  </si>
+  <si>
+    <t>924156-100-S;DD9293-100-7</t>
+  </si>
+  <si>
+    <t>6;6</t>
+  </si>
+  <si>
     <t>924156-100-S</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>0005005401</t>
-  </si>
-  <si>
-    <t>AUPU</t>
-  </si>
-  <si>
-    <t>CreateASN</t>
-  </si>
-  <si>
-    <t>InboundDelivery</t>
-  </si>
-  <si>
-    <t>GHAnnounced</t>
-  </si>
-  <si>
-    <t>GHWeighed</t>
-  </si>
-  <si>
-    <t>PutawayComplete</t>
-  </si>
-  <si>
-    <t>ASNVerify</t>
-  </si>
-  <si>
-    <t>RunAll</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>ASNID</t>
-  </si>
-  <si>
-    <t>LPNID</t>
-  </si>
-  <si>
-    <t>Pre_Allocate</t>
-  </si>
-  <si>
-    <t>Failed</t>
-  </si>
-  <si>
-    <t>1081</t>
-  </si>
-  <si>
-    <t>VGASN0824QA1320</t>
-  </si>
-  <si>
-    <t>00V08242025QA14900</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>DiversionCodeId</t>
-  </si>
-  <si>
-    <t>Num_of_Items_to_search</t>
-  </si>
-  <si>
-    <t>Search_by_Item</t>
-  </si>
-  <si>
-    <t>Search_by_Product_Type</t>
-  </si>
-  <si>
-    <t>Search_by_Missing_Dims</t>
-  </si>
-  <si>
-    <t>Apparel</t>
-  </si>
-  <si>
-    <t>Equipment</t>
-  </si>
-  <si>
-    <t>Footwear</t>
-  </si>
-  <si>
-    <t>VGASN0824QA1080</t>
-  </si>
-  <si>
-    <t>924156-100-S;420420-420-M;DD9293-100-7</t>
-  </si>
-  <si>
-    <t>6;6;6</t>
-  </si>
-  <si>
-    <t>924156-100-S;DD9293-100-7</t>
-  </si>
-  <si>
-    <t>6;6</t>
-  </si>
-  <si>
     <t>DD9293-100-7</t>
   </si>
   <si>
@@ -195,19 +201,13 @@
   </si>
   <si>
     <t>6@6;6</t>
-  </si>
-  <si>
-    <t>FirstSKU</t>
-  </si>
-  <si>
-    <t>924156-365-M</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -222,6 +222,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -285,15 +291,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -685,8 +692,8 @@
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>49</v>
+      <c r="E2" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>12</v>
@@ -744,10 +751,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s">
         <v>22</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -761,22 +783,22 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>26</v>
       </c>
     </row>
@@ -811,16 +833,16 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>31</v>
       </c>
     </row>
@@ -835,7 +857,7 @@
         <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -863,16 +885,16 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -883,10 +905,10 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F2" t="s">
         <v>22</v>
@@ -900,10 +922,10 @@
         <v>9</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F3" t="s">
         <v>22</v>
@@ -917,10 +939,10 @@
         <v>9</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F4" t="s">
         <v>22</v>
@@ -964,7 +986,7 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -991,13 +1013,13 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>13</v>
@@ -1017,13 +1039,13 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>13</v>
@@ -1043,7 +1065,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>12</v>
@@ -1069,7 +1091,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>12</v>
@@ -1095,13 +1117,13 @@
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>13</v>

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A87EF23-08C6-1F42-9B7B-88AC9E5CD9B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{732B04B2-2260-A64F-ADC4-52F86EE9BF45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="59440" yWindow="4060" windowWidth="36000" windowHeight="22500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="50">
   <si>
     <t>Plant</t>
   </si>
@@ -750,26 +750,8 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" t="s">
-        <v>22</v>
-      </c>
       <c r="F2" t="s">
         <v>22</v>
-      </c>
-      <c r="G2" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="45940" yWindow="4520" windowWidth="36000" windowHeight="22500" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="18020" yWindow="880" windowWidth="36000" windowHeight="22500" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CreateASN" sheetId="1" state="visible" r:id="rId1"/>
@@ -624,14 +624,18 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>924156-365-L</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>6</v>
+          <t>829748-010-S;829747-091-XL</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>6;6</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>2;3</t>
+        </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
@@ -646,9 +650,8 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" display="924156-100-S@DD9293-100-7" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" display="12@12" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" display="6@6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" display="12@12" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" display="6@6" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -665,7 +668,7 @@
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="14.33203125" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="9.1640625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="14.33203125" customWidth="1" min="3" max="3"/>
     <col width="12.83203125" bestFit="1" customWidth="1" min="4" max="4"/>
     <col width="16" bestFit="1" customWidth="1" min="6" max="6"/>
     <col width="9" bestFit="1" customWidth="1" min="7" max="7"/>
@@ -685,7 +688,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Exception</t>
+          <t>Exception_Input</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -715,7 +718,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="H2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -733,35 +736,43 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <cols>
+    <col width="5.5" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="11.6640625" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="17.33203125" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="97.5" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="11.6640625" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="6.1640625" bestFit="1" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Plant</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>Environment</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>ASNID</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>LPNID</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>Pre_Allocate</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>Failed</t>
         </is>
@@ -780,12 +791,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0904QA1420</t>
+          <t>VGASN0910QA9560</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V09042025QA58900;00V09042025QA36801</t>
+          <t>00V09102025QA25600;00V09102025QA72301;00V09102025QA36902;00V09102025QA95503;00V09102025QA81204</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -810,32 +821,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
-  <cols>
-    <col width="5.5" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="11.6640625" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="19.6640625" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="15" bestFit="1" customWidth="1" min="4" max="4"/>
-  </cols>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Plant</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Environment</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>LPNID</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>DiversionCodeId</t>
         </is>
@@ -854,12 +859,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>00V09022025QA65200</t>
+          <t>00V09102025QA25600</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MIXED_SKU</t>
+          <t>FIRST_SKU</t>
         </is>
       </c>
     </row>
@@ -876,12 +881,78 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>00V09022025QA95101</t>
+          <t>00V09102025QA36902</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>MIXED_SKU</t>
+          <t>STORAGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>00V09102025QA72301</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>00V09102025QA81204</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>00V09102025QA95503</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>FIRST_SKU</t>
         </is>
       </c>
     </row>
@@ -896,7 +967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="21.83203125" bestFit="1" customWidth="1" min="3" max="3"/>
@@ -955,40 +1026,9 @@
           <t>Apparel</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>1081</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>1081</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Footwear</t>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1083,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0903QA7970</t>
+          <t>VGASN0910QA9560</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="38.1640625" bestFit="1" customWidth="1" min="4" max="4"/>
@@ -1400,6 +1440,18 @@
         </is>
       </c>
       <c r="F18" s="4" t="n"/>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>VGASN0910QA2940</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>00V09102025QA28500;00V09102025QA12001;00V09102025QA14402;00V09102025QA33803;00V09102025QA33804;00V09102025QA19705;00V09102025QA97606;00V09102025QA39907;00V09102025QA69708;00V09102025QA66609;00V09102025QA46010;00V09102025QA33311;00V09102025QA16412;00V09102025QA95413;00V09102025QA68814;00V09102025QA80115;00V09102025QA83716;00V09102025QA27317;00V09102025QA96818;00V09102025QA30419</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="880" windowWidth="30240" windowHeight="19640" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="44480" yWindow="7180" windowWidth="30240" windowHeight="19640" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CreateASN" sheetId="1" state="visible" r:id="rId1"/>
@@ -116,13 +116,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="1" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -622,15 +621,15 @@
       <c r="D2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>DD9293-100-7</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>DD9293-100-11.5</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>12</v>
       </c>
-      <c r="G2" s="5" t="n">
+      <c r="G2" t="n">
         <v>6</v>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -645,11 +644,6 @@
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" display="829747-091-3XL@DD9293-100-7" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" display="12@12" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" display="6@6" r:id="rId3"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -736,32 +730,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Plant</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>Environment</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>ASNID</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>LPNID</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>Pre_Allocate</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>Failed</t>
         </is>
@@ -780,12 +774,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN1008QA4550</t>
+          <t>VGASN1010QA1810</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V10082025QA7782000;00V10082025QA6837501</t>
+          <t>00V10102025QA4058600;00V10102025QA2050401</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -820,22 +814,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Plant</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Environment</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>LPNID</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>DiversionCodeId</t>
         </is>
@@ -930,12 +924,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Apparel</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>Footwear</t>
         </is>
       </c>
     </row>

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="44480" yWindow="7180" windowWidth="30240" windowHeight="19640" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="41400" yWindow="6880" windowWidth="30240" windowHeight="19640" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CreateASN" sheetId="1" state="visible" r:id="rId1"/>
@@ -627,7 +627,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G2" t="n">
         <v>6</v>
@@ -774,12 +774,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN1010QA1810</t>
+          <t>VGASN1013QA9900</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V10102025QA4058600;00V10102025QA2050401</t>
+          <t>00V10132025QA3984800</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4F0081C-E20C-5740-B847-507BE821B835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B865DB65-CA64-354F-B14D-8306C501273E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3300" yWindow="2980" windowWidth="30240" windowHeight="19640" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="34160" windowHeight="28300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateASN" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="55">
   <si>
     <t>Plant</t>
   </si>
@@ -86,7 +86,7 @@
     <t>VG</t>
   </si>
   <si>
-    <t>303070-001-MISC</t>
+    <t>DD9293-100-7</t>
   </si>
   <si>
     <t>0005005401</t>
@@ -137,10 +137,10 @@
     <t>1081</t>
   </si>
   <si>
-    <t>VGASN1014QA9020</t>
-  </si>
-  <si>
-    <t>00V10142025QA8107600;00V10142025QA7725701</t>
+    <t>VGASN1023QA3490</t>
+  </si>
+  <si>
+    <t>00V10232025QA5520800</t>
   </si>
   <si>
     <t>N</t>
@@ -149,12 +149,6 @@
     <t>DiversionCodeId</t>
   </si>
   <si>
-    <t>00V10072025QA3758700</t>
-  </si>
-  <si>
-    <t>IN_VAS</t>
-  </si>
-  <si>
     <t>Num_of_Items_to_search</t>
   </si>
   <si>
@@ -167,68 +161,68 @@
     <t>Search_by_Missing_Dims</t>
   </si>
   <si>
+    <t>Apparel</t>
+  </si>
+  <si>
+    <t>VGASN0910QA9560</t>
+  </si>
+  <si>
+    <t>924156-100-S;420420-420-M;DD9293-100-7</t>
+  </si>
+  <si>
+    <t>6;6;6</t>
+  </si>
+  <si>
+    <t>924156-100-S</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>924156-100-S@420420-420-M;DD9293-100-7</t>
+  </si>
+  <si>
+    <t>12@12;12</t>
+  </si>
+  <si>
+    <t>6@6;6</t>
+  </si>
+  <si>
+    <t>829748-010-4XL</t>
+  </si>
+  <si>
+    <t>829747-091-M-T</t>
+  </si>
+  <si>
+    <t>DD9293-100-11.5</t>
+  </si>
+  <si>
+    <t>DD9293-100-6</t>
+  </si>
+  <si>
+    <t>Item Search Backup</t>
+  </si>
+  <si>
+    <t>Equipment</t>
+  </si>
+  <si>
     <t>Footwear</t>
   </si>
   <si>
-    <t>VGASN0910QA9560</t>
-  </si>
-  <si>
-    <t>924156-100-S;420420-420-M;DD9293-100-7</t>
-  </si>
-  <si>
-    <t>6;6;6</t>
-  </si>
-  <si>
-    <t>924156-100-S</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>DD9293-100-7</t>
-  </si>
-  <si>
-    <t>924156-100-S@420420-420-M;DD9293-100-7</t>
-  </si>
-  <si>
-    <t>12@12;12</t>
-  </si>
-  <si>
-    <t>6@6;6</t>
-  </si>
-  <si>
-    <t>829748-010-4XL</t>
-  </si>
-  <si>
-    <t>829747-091-M-T</t>
-  </si>
-  <si>
-    <t>DD9293-100-11.5</t>
-  </si>
-  <si>
-    <t>DD9293-100-6</t>
-  </si>
-  <si>
-    <t>Item Search Backup</t>
-  </si>
-  <si>
-    <t>Apparel</t>
-  </si>
-  <si>
-    <t>Equipment</t>
-  </si>
-  <si>
     <t>VGASN1007QA6890</t>
   </si>
   <si>
     <t>00V10072025QA8017900;00V10072025QA7380501</t>
+  </si>
+  <si>
+    <t>MEASUREMENT</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -260,6 +254,12 @@
       <b/>
       <sz val="12"/>
       <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="9.8000000000000007"/>
+      <color rgb="FF6AAB73"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -313,7 +313,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
@@ -325,6 +325,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -714,14 +715,14 @@
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F2">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="G2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>12</v>
@@ -776,12 +777,6 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
       <c r="E2" t="s">
         <v>22</v>
       </c>
@@ -803,22 +798,22 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>26</v>
       </c>
     </row>
@@ -859,16 +854,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>31</v>
       </c>
     </row>
@@ -880,10 +875,10 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D2" t="s">
-        <v>33</v>
+        <v>29</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -911,16 +906,16 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" t="s">
         <v>34</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>35</v>
-      </c>
-      <c r="E1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -934,7 +929,10 @@
         <v>2</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
+      </c>
+      <c r="F2" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -972,7 +970,7 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -999,13 +997,13 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>12</v>
@@ -1042,13 +1040,13 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>12</v>
@@ -1068,13 +1066,13 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>12</v>
@@ -1094,13 +1092,13 @@
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>12</v>
@@ -1111,27 +1109,27 @@
     </row>
     <row r="6" spans="1:8">
       <c r="D6" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="D7" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="D8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="D9" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1142,16 +1140,16 @@
         <v>1</v>
       </c>
       <c r="C15" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="F15" s="4" t="s">
         <v>35</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1166,7 +1164,7 @@
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="F16" s="4"/>
     </row>
@@ -1182,7 +1180,7 @@
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F17" s="4"/>
     </row>
@@ -1198,16 +1196,16 @@
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="F18" s="4"/>
     </row>
     <row r="22" spans="1:10">
       <c r="D22" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E22" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31" spans="1:10">

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B865DB65-CA64-354F-B14D-8306C501273E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B51F78FE-0513-5245-B6EF-90FF561E5BA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="34160" windowHeight="28300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="36000" yWindow="500" windowWidth="34160" windowHeight="28300" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateASN" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="58">
   <si>
     <t>Plant</t>
   </si>
@@ -137,16 +137,28 @@
     <t>1081</t>
   </si>
   <si>
-    <t>VGASN1023QA3490</t>
+    <t>VGASN1025QA1710</t>
+  </si>
+  <si>
+    <t>00V10252025QA5767100;00V10252025QA3139301</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>VGASN1025QA3651</t>
+  </si>
+  <si>
+    <t>00V10252025QA8991102</t>
+  </si>
+  <si>
+    <t>DiversionCodeId</t>
   </si>
   <si>
     <t>00V10232025QA5520800</t>
   </si>
   <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>DiversionCodeId</t>
+    <t>MEASUREMENT</t>
   </si>
   <si>
     <t>Num_of_Items_to_search</t>
@@ -213,9 +225,6 @@
   </si>
   <si>
     <t>00V10072025QA8017900;00V10072025QA7380501</t>
-  </si>
-  <si>
-    <t>MEASUREMENT</t>
   </si>
 </sst>
 </file>
@@ -251,15 +260,15 @@
       <name val="Aptos Narrow"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <name val="Aptos Narrow"/>
-    </font>
-    <font>
       <sz val="9.8000000000000007"/>
       <color rgb="FF6AAB73"/>
       <name val="JetBrains Mono"/>
       <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Aptos Narrow"/>
     </font>
   </fonts>
   <fills count="2">
@@ -322,10 +331,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -713,7 +722,7 @@
         <v>10</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>11</v>
@@ -777,13 +786,7 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="E2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="A2" t="s">
         <v>22</v>
       </c>
     </row>
@@ -794,26 +797,26 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="7" t="s">
         <v>26</v>
       </c>
     </row>
@@ -834,6 +837,26 @@
         <v>22</v>
       </c>
       <c r="F2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" t="s">
         <v>30</v>
       </c>
     </row>
@@ -854,17 +877,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>31</v>
+      <c r="D1" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -875,10 +898,10 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>54</v>
+        <v>34</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -888,7 +911,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="3" max="3" width="21.83203125" bestFit="1" customWidth="1"/>
@@ -906,16 +929,16 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -929,10 +952,35 @@
         <v>2</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F2" t="s">
-        <v>22</v>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>1081</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>1081</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -970,7 +1018,7 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -997,13 +1045,13 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>12</v>
@@ -1040,13 +1088,13 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>12</v>
@@ -1069,10 +1117,10 @@
         <v>11</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>12</v>
@@ -1092,13 +1140,13 @@
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>12</v>
@@ -1109,27 +1157,27 @@
     </row>
     <row r="6" spans="1:8">
       <c r="D6" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="D7" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="D8" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="D9" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1140,16 +1188,16 @@
         <v>1</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1164,7 +1212,7 @@
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F16" s="4"/>
     </row>
@@ -1180,7 +1228,7 @@
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F17" s="4"/>
     </row>
@@ -1196,16 +1244,16 @@
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F18" s="4"/>
     </row>
     <row r="22" spans="1:10">
       <c r="D22" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E22" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31" spans="1:10">

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B51F78FE-0513-5245-B6EF-90FF561E5BA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E6ADAF9-2D73-AA45-8FBF-C853474387C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="36000" yWindow="500" windowWidth="34160" windowHeight="28300" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="57">
   <si>
     <t>Plant</t>
   </si>
@@ -86,111 +86,114 @@
     <t>VG</t>
   </si>
   <si>
+    <t>136027-115-9.5</t>
+  </si>
+  <si>
+    <t>0005005401</t>
+  </si>
+  <si>
+    <t>AUPU</t>
+  </si>
+  <si>
+    <t>CreateASN</t>
+  </si>
+  <si>
+    <t>InboundDelivery</t>
+  </si>
+  <si>
+    <t>Exception_Input</t>
+  </si>
+  <si>
+    <t>GHAnnounced</t>
+  </si>
+  <si>
+    <t>GHWeighed</t>
+  </si>
+  <si>
+    <t>PutawayComplete</t>
+  </si>
+  <si>
+    <t>ASNVerify</t>
+  </si>
+  <si>
+    <t>RunAll</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>ASNID</t>
+  </si>
+  <si>
+    <t>LPNID</t>
+  </si>
+  <si>
+    <t>Pre_Allocate</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
+    <t>1081</t>
+  </si>
+  <si>
+    <t>VGASN1104QA1040</t>
+  </si>
+  <si>
+    <t>00V11042025QA1783600;00V11042025QA6105801</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>DiversionCodeId</t>
+  </si>
+  <si>
+    <t>00V10232025QA5520800</t>
+  </si>
+  <si>
+    <t>MEASUREMENT</t>
+  </si>
+  <si>
+    <t>Num_of_Items_to_search</t>
+  </si>
+  <si>
+    <t>Search_by_Item</t>
+  </si>
+  <si>
+    <t>Search_by_Product_Type</t>
+  </si>
+  <si>
+    <t>Search_by_Missing_Dims</t>
+  </si>
+  <si>
+    <t>Apparel</t>
+  </si>
+  <si>
+    <t>Equipment</t>
+  </si>
+  <si>
+    <t>Footwear</t>
+  </si>
+  <si>
+    <t>VGASN0910QA9560</t>
+  </si>
+  <si>
+    <t>924156-100-S;420420-420-M;DD9293-100-7</t>
+  </si>
+  <si>
+    <t>6;6;6</t>
+  </si>
+  <si>
+    <t>924156-100-S</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
     <t>DD9293-100-7</t>
   </si>
   <si>
-    <t>0005005401</t>
-  </si>
-  <si>
-    <t>AUPU</t>
-  </si>
-  <si>
-    <t>CreateASN</t>
-  </si>
-  <si>
-    <t>InboundDelivery</t>
-  </si>
-  <si>
-    <t>Exception_Input</t>
-  </si>
-  <si>
-    <t>GHAnnounced</t>
-  </si>
-  <si>
-    <t>GHWeighed</t>
-  </si>
-  <si>
-    <t>PutawayComplete</t>
-  </si>
-  <si>
-    <t>ASNVerify</t>
-  </si>
-  <si>
-    <t>RunAll</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>ASNID</t>
-  </si>
-  <si>
-    <t>LPNID</t>
-  </si>
-  <si>
-    <t>Pre_Allocate</t>
-  </si>
-  <si>
-    <t>Failed</t>
-  </si>
-  <si>
-    <t>1081</t>
-  </si>
-  <si>
-    <t>VGASN1025QA1710</t>
-  </si>
-  <si>
-    <t>00V10252025QA5767100;00V10252025QA3139301</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>VGASN1025QA3651</t>
-  </si>
-  <si>
-    <t>00V10252025QA8991102</t>
-  </si>
-  <si>
-    <t>DiversionCodeId</t>
-  </si>
-  <si>
-    <t>00V10232025QA5520800</t>
-  </si>
-  <si>
-    <t>MEASUREMENT</t>
-  </si>
-  <si>
-    <t>Num_of_Items_to_search</t>
-  </si>
-  <si>
-    <t>Search_by_Item</t>
-  </si>
-  <si>
-    <t>Search_by_Product_Type</t>
-  </si>
-  <si>
-    <t>Search_by_Missing_Dims</t>
-  </si>
-  <si>
-    <t>Apparel</t>
-  </si>
-  <si>
-    <t>VGASN0910QA9560</t>
-  </si>
-  <si>
-    <t>924156-100-S;420420-420-M;DD9293-100-7</t>
-  </si>
-  <si>
-    <t>6;6;6</t>
-  </si>
-  <si>
-    <t>924156-100-S</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
     <t>924156-100-S@420420-420-M;DD9293-100-7</t>
   </si>
   <si>
@@ -213,12 +216,6 @@
   </si>
   <si>
     <t>Item Search Backup</t>
-  </si>
-  <si>
-    <t>Equipment</t>
-  </si>
-  <si>
-    <t>Footwear</t>
   </si>
   <si>
     <t>VGASN1007QA6890</t>
@@ -722,13 +719,13 @@
         <v>10</v>
       </c>
       <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
         <v>11</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>6</v>
@@ -789,6 +786,9 @@
       <c r="A2" t="s">
         <v>22</v>
       </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -797,7 +797,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -837,26 +837,6 @@
         <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" t="s">
         <v>30</v>
       </c>
     </row>
@@ -887,7 +867,7 @@
         <v>24</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -898,10 +878,10 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -929,16 +909,16 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" t="s">
         <v>36</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>37</v>
-      </c>
-      <c r="E1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F1" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -949,11 +929,12 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>40</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" s="4"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
@@ -963,11 +944,12 @@
         <v>9</v>
       </c>
       <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>54</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" s="4"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
@@ -977,11 +959,12 @@
         <v>9</v>
       </c>
       <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>55</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1114,7 +1097,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>45</v>
@@ -1140,13 +1123,13 @@
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>12</v>
@@ -1157,27 +1140,27 @@
     </row>
     <row r="6" spans="1:8">
       <c r="D6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="D7" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="D8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="D9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1188,16 +1171,16 @@
         <v>1</v>
       </c>
       <c r="C15" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="F15" s="4" t="s">
         <v>37</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1212,7 +1195,7 @@
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F16" s="4"/>
     </row>
@@ -1228,7 +1211,7 @@
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="F17" s="4"/>
     </row>
@@ -1244,16 +1227,16 @@
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="F18" s="4"/>
     </row>
     <row r="22" spans="1:10">
       <c r="D22" t="s">
+        <v>55</v>
+      </c>
+      <c r="E22" t="s">
         <v>56</v>
-      </c>
-      <c r="E22" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="31" spans="1:10">

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E6ADAF9-2D73-AA45-8FBF-C853474387C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F66FD58-DA3B-AA47-BE5F-F1F88842551C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36000" yWindow="500" windowWidth="34160" windowHeight="28300" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38240" yWindow="4040" windowWidth="36000" windowHeight="22500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateASN" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="70">
   <si>
     <t>Plant</t>
   </si>
@@ -86,7 +86,13 @@
     <t>VG</t>
   </si>
   <si>
-    <t>136027-115-9.5</t>
+    <t>136027-115-9.5;829747-091-S-T;829747-091-S-T@136027-115-9.5</t>
+  </si>
+  <si>
+    <t>30;12;12@12</t>
+  </si>
+  <si>
+    <t>6;6;6@6</t>
   </si>
   <si>
     <t>0005005401</t>
@@ -137,10 +143,10 @@
     <t>1081</t>
   </si>
   <si>
-    <t>VGASN1104QA1040</t>
-  </si>
-  <si>
-    <t>00V11042025QA1783600;00V11042025QA6105801</t>
+    <t>VGASN1107QA2830</t>
+  </si>
+  <si>
+    <t>00V11072025QA6969400;00V11072025QA8085801;00V11072025QA6618802;00V11072025QA3998003;00V11072025QA5036804;00V11072025QA1481505;00V11072025QA7682306;00V11072025QA7690607;00V11072025QA1452008</t>
   </si>
   <si>
     <t>N</t>
@@ -149,12 +155,45 @@
     <t>DiversionCodeId</t>
   </si>
   <si>
-    <t>00V10232025QA5520800</t>
+    <t>00V11072025QA1452008</t>
+  </si>
+  <si>
+    <t>MIXED_SKU</t>
+  </si>
+  <si>
+    <t>00V11072025QA1481505</t>
+  </si>
+  <si>
+    <t>FIRST_SKU</t>
+  </si>
+  <si>
+    <t>00V11072025QA3998003</t>
+  </si>
+  <si>
+    <t>IN_VAS</t>
+  </si>
+  <si>
+    <t>00V11072025QA5036804</t>
   </si>
   <si>
     <t>MEASUREMENT</t>
   </si>
   <si>
+    <t>00V11072025QA6618802</t>
+  </si>
+  <si>
+    <t>00V11072025QA6969400</t>
+  </si>
+  <si>
+    <t>00V11072025QA7682306</t>
+  </si>
+  <si>
+    <t>00V11072025QA7690607</t>
+  </si>
+  <si>
+    <t>00V11072025QA8085801</t>
+  </si>
+  <si>
     <t>Num_of_Items_to_search</t>
   </si>
   <si>
@@ -167,6 +206,48 @@
     <t>Search_by_Missing_Dims</t>
   </si>
   <si>
+    <t>VGASN0910QA9560</t>
+  </si>
+  <si>
+    <t>924156-100-S;420420-420-M;DD9293-100-7</t>
+  </si>
+  <si>
+    <t>6;6;6</t>
+  </si>
+  <si>
+    <t>924156-100-S</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>DD9293-100-7</t>
+  </si>
+  <si>
+    <t>924156-100-S@420420-420-M;DD9293-100-7</t>
+  </si>
+  <si>
+    <t>12@12;12</t>
+  </si>
+  <si>
+    <t>6@6;6</t>
+  </si>
+  <si>
+    <t>829748-010-4XL</t>
+  </si>
+  <si>
+    <t>829747-091-M-T</t>
+  </si>
+  <si>
+    <t>DD9293-100-11.5</t>
+  </si>
+  <si>
+    <t>DD9293-100-6</t>
+  </si>
+  <si>
+    <t>Item Search Backup</t>
+  </si>
+  <si>
     <t>Apparel</t>
   </si>
   <si>
@@ -174,48 +255,6 @@
   </si>
   <si>
     <t>Footwear</t>
-  </si>
-  <si>
-    <t>VGASN0910QA9560</t>
-  </si>
-  <si>
-    <t>924156-100-S;420420-420-M;DD9293-100-7</t>
-  </si>
-  <si>
-    <t>6;6;6</t>
-  </si>
-  <si>
-    <t>924156-100-S</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>DD9293-100-7</t>
-  </si>
-  <si>
-    <t>924156-100-S@420420-420-M;DD9293-100-7</t>
-  </si>
-  <si>
-    <t>12@12;12</t>
-  </si>
-  <si>
-    <t>6@6;6</t>
-  </si>
-  <si>
-    <t>829748-010-4XL</t>
-  </si>
-  <si>
-    <t>829747-091-M-T</t>
-  </si>
-  <si>
-    <t>DD9293-100-11.5</t>
-  </si>
-  <si>
-    <t>DD9293-100-6</t>
-  </si>
-  <si>
-    <t>Item Search Backup</t>
   </si>
   <si>
     <t>VGASN1007QA6890</t>
@@ -228,7 +267,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -255,12 +294,6 @@
       <b/>
       <sz val="12"/>
       <name val="Aptos Narrow"/>
-    </font>
-    <font>
-      <sz val="9.8000000000000007"/>
-      <color rgb="FF6AAB73"/>
-      <name val="JetBrains Mono"/>
-      <family val="3"/>
     </font>
     <font>
       <b/>
@@ -319,7 +352,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
@@ -328,8 +361,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -724,17 +756,17 @@
       <c r="E2" t="s">
         <v>11</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="s">
         <v>12</v>
       </c>
-      <c r="G2">
-        <v>6</v>
+      <c r="G2" t="s">
+        <v>13</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -758,36 +790,33 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
+      <c r="D2" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -801,43 +830,43 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="7" t="s">
+      <c r="C1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="D1" s="5" t="s">
         <v>26</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -847,7 +876,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="5.5" bestFit="1" customWidth="1"/>
@@ -857,31 +886,143 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>31</v>
+      <c r="C1" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="D2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -909,16 +1050,16 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E1" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="F1" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -931,39 +1072,15 @@
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2" t="s">
-        <v>46</v>
-      </c>
       <c r="E2" s="4"/>
+      <c r="F2" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3">
-        <v>1081</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
-        <v>44</v>
-      </c>
       <c r="E3" s="4"/>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4">
-        <v>1081</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
       <c r="E4" s="4"/>
     </row>
   </sheetData>
@@ -990,7 +1107,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1001,7 +1118,7 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1028,19 +1145,19 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1054,10 +1171,10 @@
         <v>1</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1071,19 +1188,19 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1097,19 +1214,19 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1123,44 +1240,44 @@
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="D6" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="D7" s="1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="D8" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="D9" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1171,16 +1288,16 @@
         <v>1</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1195,7 +1312,7 @@
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="F16" s="4"/>
     </row>
@@ -1211,7 +1328,7 @@
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="F17" s="4"/>
     </row>
@@ -1227,16 +1344,16 @@
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4" t="s">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="F18" s="4"/>
     </row>
     <row r="22" spans="1:10">
       <c r="D22" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="E22" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31" spans="1:10">

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F66FD58-DA3B-AA47-BE5F-F1F88842551C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8504E9D-A212-6144-BBE6-2D61D0B90DE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38240" yWindow="4040" windowWidth="36000" windowHeight="22500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38120" yWindow="-3100" windowWidth="36000" windowHeight="21100" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateASN" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="57">
   <si>
     <t>Plant</t>
   </si>
@@ -86,13 +86,7 @@
     <t>VG</t>
   </si>
   <si>
-    <t>136027-115-9.5;829747-091-S-T;829747-091-S-T@136027-115-9.5</t>
-  </si>
-  <si>
-    <t>30;12;12@12</t>
-  </si>
-  <si>
-    <t>6;6;6@6</t>
+    <t>DD9293-100-7</t>
   </si>
   <si>
     <t>0005005401</t>
@@ -143,10 +137,7 @@
     <t>1081</t>
   </si>
   <si>
-    <t>VGASN1107QA2830</t>
-  </si>
-  <si>
-    <t>00V11072025QA6969400;00V11072025QA8085801;00V11072025QA6618802;00V11072025QA3998003;00V11072025QA5036804;00V11072025QA1481505;00V11072025QA7682306;00V11072025QA7690607;00V11072025QA1452008</t>
+    <t>00V11132025QA5308300;00V11132025QA8216301</t>
   </si>
   <si>
     <t>N</t>
@@ -155,43 +146,16 @@
     <t>DiversionCodeId</t>
   </si>
   <si>
-    <t>00V11072025QA1452008</t>
-  </si>
-  <si>
-    <t>MIXED_SKU</t>
-  </si>
-  <si>
-    <t>00V11072025QA1481505</t>
-  </si>
-  <si>
-    <t>FIRST_SKU</t>
-  </si>
-  <si>
-    <t>00V11072025QA3998003</t>
-  </si>
-  <si>
-    <t>IN_VAS</t>
-  </si>
-  <si>
-    <t>00V11072025QA5036804</t>
+    <t>00V11132025QA5308300</t>
   </si>
   <si>
     <t>MEASUREMENT</t>
   </si>
   <si>
-    <t>00V11072025QA6618802</t>
-  </si>
-  <si>
-    <t>00V11072025QA6969400</t>
-  </si>
-  <si>
-    <t>00V11072025QA7682306</t>
-  </si>
-  <si>
-    <t>00V11072025QA7690607</t>
-  </si>
-  <si>
-    <t>00V11072025QA8085801</t>
+    <t>00V11132025QA8216301</t>
+  </si>
+  <si>
+    <t>STORAGE</t>
   </si>
   <si>
     <t>Num_of_Items_to_search</t>
@@ -206,7 +170,7 @@
     <t>Search_by_Missing_Dims</t>
   </si>
   <si>
-    <t>VGASN0910QA9560</t>
+    <t>Equipment</t>
   </si>
   <si>
     <t>924156-100-S;420420-420-M;DD9293-100-7</t>
@@ -221,9 +185,6 @@
     <t>6</t>
   </si>
   <si>
-    <t>DD9293-100-7</t>
-  </si>
-  <si>
     <t>924156-100-S@420420-420-M;DD9293-100-7</t>
   </si>
   <si>
@@ -251,9 +212,6 @@
     <t>Apparel</t>
   </si>
   <si>
-    <t>Equipment</t>
-  </si>
-  <si>
     <t>Footwear</t>
   </si>
   <si>
@@ -261,6 +219,9 @@
   </si>
   <si>
     <t>00V10072025QA8017900;00V10072025QA7380501</t>
+  </si>
+  <si>
+    <t>0215055293</t>
   </si>
 </sst>
 </file>
@@ -352,7 +313,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
@@ -364,6 +325,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -753,20 +715,20 @@
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2">
         <v>12</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2">
+        <v>6</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" t="s">
         <v>13</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -790,33 +752,39 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>19</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>20</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>21</v>
       </c>
-      <c r="G1" t="s">
+    </row>
+    <row r="2" spans="1:8">
+      <c r="E2" t="s">
         <v>22</v>
       </c>
-      <c r="H1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="D2" t="s">
-        <v>24</v>
+      <c r="F2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -828,6 +796,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="43.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="5" t="s">
@@ -837,36 +813,36 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" t="s">
         <v>29</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2" t="s">
-        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -876,14 +852,8 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
-  <cols>
-    <col min="1" max="1" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="6" t="s">
@@ -893,136 +863,38 @@
         <v>1</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" t="s">
-        <v>46</v>
-      </c>
-      <c r="D10" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1032,7 +904,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="3" max="3" width="21.83203125" bestFit="1" customWidth="1"/>
@@ -1050,16 +922,16 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="D1" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="E1" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="F1" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -1070,18 +942,11 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="E2" s="4"/>
-      <c r="F2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="E3" s="4"/>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="E4" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>39</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1107,7 +972,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1117,8 +982,8 @@
       <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s">
-        <v>51</v>
+      <c r="C2" s="7" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1145,19 +1010,19 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1171,10 +1036,10 @@
         <v>1</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1188,19 +1053,19 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1214,19 +1079,19 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1240,44 +1105,44 @@
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="D6" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="D7" s="1" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="D8" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="D9" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1288,16 +1153,16 @@
         <v>1</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1312,7 +1177,7 @@
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="F16" s="4"/>
     </row>
@@ -1328,7 +1193,7 @@
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="F17" s="4"/>
     </row>
@@ -1344,16 +1209,16 @@
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="F18" s="4"/>
     </row>
     <row r="22" spans="1:10">
       <c r="D22" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="E22" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:10">

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8504E9D-A212-6144-BBE6-2D61D0B90DE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BE505E9-0D05-D741-B92B-8DCC9C419FF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38120" yWindow="-3100" windowWidth="36000" windowHeight="21100" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateASN" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="59">
   <si>
     <t>Plant</t>
   </si>
@@ -222,6 +222,12 @@
   </si>
   <si>
     <t>0215055293</t>
+  </si>
+  <si>
+    <t>Search_by_Style</t>
+  </si>
+  <si>
+    <t>Search_by_Color</t>
   </si>
 </sst>
 </file>
@@ -904,7 +910,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="3" max="3" width="21.83203125" bestFit="1" customWidth="1"/>
@@ -912,9 +918,10 @@
     <col min="5" max="5" width="19.83203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -933,8 +940,14 @@
       <c r="F1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2">
         <v>1081</v>
       </c>

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BE505E9-0D05-D741-B92B-8DCC9C419FF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A27A2A1E-3E64-9B4F-8388-E29A06A807C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AD288C2-16B1-C84F-8750-2244AA5CABAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC006C0-4F95-CE4D-98A1-B18519C41C4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateASN" sheetId="1" r:id="rId1"/>
@@ -21,20 +21,7 @@
     <sheet name="SearchASN" sheetId="6" r:id="rId6"/>
     <sheet name="BackUP" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -64,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="78">
   <si>
     <t>Plant</t>
   </si>
@@ -96,10 +83,7 @@
     <t>QA</t>
   </si>
   <si>
-    <t>VG</t>
-  </si>
-  <si>
-    <t>927205-043-S</t>
+    <t>432997-128-10</t>
   </si>
   <si>
     <t>0005005401</t>
@@ -150,9 +134,6 @@
     <t>1081</t>
   </si>
   <si>
-    <t>00V12042025QA3274100</t>
-  </si>
-  <si>
     <t>N</t>
   </si>
   <si>
@@ -186,6 +167,63 @@
     <t>Search_by_Color</t>
   </si>
   <si>
+    <t>709506-010-4XL-T</t>
+  </si>
+  <si>
+    <t>709506-010-XL-T</t>
+  </si>
+  <si>
+    <t>709506-010-S-T</t>
+  </si>
+  <si>
+    <t>709506-010-S</t>
+  </si>
+  <si>
+    <t>709506-010-2XL</t>
+  </si>
+  <si>
+    <t>709506-010-3XL-T</t>
+  </si>
+  <si>
+    <t>HJ4186-010-MISC</t>
+  </si>
+  <si>
+    <t>HJ8178-010-MISC</t>
+  </si>
+  <si>
+    <t>HV6626-229-MISC</t>
+  </si>
+  <si>
+    <t>IB6207-229-MISC</t>
+  </si>
+  <si>
+    <t>II5196-031-MISC</t>
+  </si>
+  <si>
+    <t>II5196-405-MISC</t>
+  </si>
+  <si>
+    <t>343880-202-14</t>
+  </si>
+  <si>
+    <t>343880-202-13</t>
+  </si>
+  <si>
+    <t>343880-202-8</t>
+  </si>
+  <si>
+    <t>343880-202-10</t>
+  </si>
+  <si>
+    <t>343880-202-11</t>
+  </si>
+  <si>
+    <t>343880-202-9</t>
+  </si>
+  <si>
+    <t>0215055465</t>
+  </si>
+  <si>
     <t>924156-100-S;420420-420-M;DD9293-100-7</t>
   </si>
   <si>
@@ -243,25 +281,10 @@
     <t>829748-010-4XL@829747-091-M-T</t>
   </si>
   <si>
-    <t>0215055465</t>
-  </si>
-  <si>
-    <t>0215055370</t>
-  </si>
-  <si>
-    <t>343738-031-1Y</t>
-  </si>
-  <si>
-    <t>343738-031-2Y</t>
-  </si>
-  <si>
-    <t>343738-031-11C</t>
-  </si>
-  <si>
-    <t>343738-031-12C</t>
-  </si>
-  <si>
-    <t>343738-031-1.5Y</t>
+    <t>0215055492;0215055325;0215055444;0215055326;0215055445</t>
+  </si>
+  <si>
+    <t>00009369430000189413;00027112400000181326;00033324160000421528;00018335030000996223;00048562010000569466;T4121020250000000004;T4121020250000000005;T4121020250000000006;T4121020250000000007;T4121020250000000008;</t>
   </si>
 </sst>
 </file>
@@ -750,26 +773,26 @@
       <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s">
-        <v>10</v>
+      <c r="C2">
+        <v>81</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F2" s="6">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G2" s="6">
         <v>6</v>
       </c>
       <c r="H2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" t="s">
         <v>12</v>
-      </c>
-      <c r="I2" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -798,33 +821,33 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" t="s">
         <v>14</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>15</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>16</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>17</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>18</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>19</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>20</v>
       </c>
-      <c r="H1" t="s">
+    </row>
+    <row r="2" spans="1:8">
+      <c r="B2" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="D2" t="s">
-        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -836,9 +859,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
-  <cols>
-    <col min="3" max="3" width="24.5" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="8" t="s">
@@ -848,36 +868,34 @@
         <v>1</v>
       </c>
       <c r="C1" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="E1" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="F1" s="8" t="s">
         <v>25</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="5"/>
+      <c r="D2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
         <v>27</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -898,38 +916,38 @@
         <v>1</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -939,7 +957,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="3" max="3" width="21.83203125" bestFit="1" customWidth="1"/>
@@ -958,22 +976,22 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" t="s">
         <v>34</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>35</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>36</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>37</v>
-      </c>
-      <c r="G1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H1" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -984,7 +1002,7 @@
         <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="E2" s="4"/>
     </row>
@@ -996,7 +1014,7 @@
         <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1007,7 +1025,7 @@
         <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1018,7 +1036,7 @@
         <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1029,7 +1047,150 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>65</v>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7">
+        <v>1081</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8">
+        <v>1081</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9">
+        <v>1081</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10">
+        <v>1081</v>
+      </c>
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11">
+        <v>1081</v>
+      </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12">
+        <v>1081</v>
+      </c>
+      <c r="B12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13">
+        <v>1081</v>
+      </c>
+      <c r="B13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14">
+        <v>1081</v>
+      </c>
+      <c r="B14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15">
+        <v>1081</v>
+      </c>
+      <c r="B15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16">
+        <v>1081</v>
+      </c>
+      <c r="B16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17">
+        <v>1081</v>
+      </c>
+      <c r="B17" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18">
+        <v>1081</v>
+      </c>
+      <c r="B18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19">
+        <v>1081</v>
+      </c>
+      <c r="B19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -1056,7 +1217,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1067,7 +1228,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1094,19 +1255,19 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="G1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
         <v>12</v>
-      </c>
-      <c r="H1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1120,10 +1281,10 @@
         <v>1</v>
       </c>
       <c r="G2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" t="s">
         <v>12</v>
-      </c>
-      <c r="H2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1137,19 +1298,19 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="G3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" t="s">
         <v>12</v>
-      </c>
-      <c r="H3" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1163,19 +1324,19 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" t="s">
         <v>12</v>
-      </c>
-      <c r="H4" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1189,44 +1350,44 @@
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="G5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" t="s">
         <v>12</v>
-      </c>
-      <c r="H5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="D6" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="D7" s="1" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="D8" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="D9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1237,16 +1398,16 @@
         <v>1</v>
       </c>
       <c r="C15" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="F15" s="4" t="s">
         <v>35</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1261,7 +1422,7 @@
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="F16" s="4"/>
     </row>
@@ -1277,7 +1438,7 @@
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="F17" s="4"/>
     </row>
@@ -1293,21 +1454,26 @@
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="F18" s="4"/>
     </row>
     <row r="22" spans="1:10">
       <c r="D22" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="E22" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="D25" s="6" t="s">
-        <v>58</v>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="D26" s="5" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="31" spans="1:10">

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC006C0-4F95-CE4D-98A1-B18519C41C4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0A9E3D9-7C15-F34F-BA6D-92CA3B2EBE96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="60">
   <si>
     <t>Plant</t>
   </si>
@@ -83,7 +83,10 @@
     <t>QA</t>
   </si>
   <si>
-    <t>432997-128-10</t>
+    <t>VG</t>
+  </si>
+  <si>
+    <t>AJ7566-010-LT</t>
   </si>
   <si>
     <t>0005005401</t>
@@ -167,61 +170,7 @@
     <t>Search_by_Color</t>
   </si>
   <si>
-    <t>709506-010-4XL-T</t>
-  </si>
-  <si>
-    <t>709506-010-XL-T</t>
-  </si>
-  <si>
-    <t>709506-010-S-T</t>
-  </si>
-  <si>
-    <t>709506-010-S</t>
-  </si>
-  <si>
-    <t>709506-010-2XL</t>
-  </si>
-  <si>
-    <t>709506-010-3XL-T</t>
-  </si>
-  <si>
-    <t>HJ4186-010-MISC</t>
-  </si>
-  <si>
-    <t>HJ8178-010-MISC</t>
-  </si>
-  <si>
-    <t>HV6626-229-MISC</t>
-  </si>
-  <si>
-    <t>IB6207-229-MISC</t>
-  </si>
-  <si>
-    <t>II5196-031-MISC</t>
-  </si>
-  <si>
-    <t>II5196-405-MISC</t>
-  </si>
-  <si>
-    <t>343880-202-14</t>
-  </si>
-  <si>
-    <t>343880-202-13</t>
-  </si>
-  <si>
-    <t>343880-202-8</t>
-  </si>
-  <si>
-    <t>343880-202-10</t>
-  </si>
-  <si>
-    <t>343880-202-11</t>
-  </si>
-  <si>
-    <t>343880-202-9</t>
-  </si>
-  <si>
-    <t>0215055465</t>
+    <t>Footwear</t>
   </si>
   <si>
     <t>924156-100-S;420420-420-M;DD9293-100-7</t>
@@ -269,9 +218,6 @@
     <t>Equipment</t>
   </si>
   <si>
-    <t>Footwear</t>
-  </si>
-  <si>
     <t>VGASN1126QA8010</t>
   </si>
   <si>
@@ -281,10 +227,10 @@
     <t>829748-010-4XL@829747-091-M-T</t>
   </si>
   <si>
-    <t>0215055492;0215055325;0215055444;0215055326;0215055445</t>
-  </si>
-  <si>
-    <t>00009369430000189413;00027112400000181326;00033324160000421528;00018335030000996223;00048562010000569466;T4121020250000000004;T4121020250000000005;T4121020250000000006;T4121020250000000007;T4121020250000000008;</t>
+    <t>VGASN1212QA2170;VGASN1212QA3730;VGASN1212QA4190;VGASN1212QA1710</t>
+  </si>
+  <si>
+    <t>0215055531</t>
   </si>
 </sst>
 </file>
@@ -376,7 +322,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
@@ -386,6 +332,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -725,7 +680,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
@@ -773,34 +728,39 @@
       <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="C2">
-        <v>81</v>
+      <c r="C2" t="s">
+        <v>10</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="6">
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="8">
+        <v>36</v>
+      </c>
+      <c r="G2" s="8">
+        <v>6</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="6">
-        <v>6</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="I2" t="s">
-        <v>12</v>
-      </c>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="3"/>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="3"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" display="104265-039-9@030588-010-L;927205-043-S" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="F2" r:id="rId2" display="12@12;12" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="G2" r:id="rId3" display="6@6;6" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -821,33 +781,45 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="B2" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -861,41 +833,40 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D1" s="8" t="s">
+      <c r="C1" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="D1" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="E1" s="11" t="s">
         <v>25</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" t="s">
-        <v>77</v>
+      <c r="C2" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -916,38 +887,38 @@
         <v>1</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
       </c>
       <c r="C3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" t="s">
         <v>31</v>
-      </c>
-      <c r="D3" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -957,7 +928,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="3" max="3" width="21.83203125" bestFit="1" customWidth="1"/>
@@ -976,22 +947,22 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1001,196 +972,11 @@
       <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E2" s="4"/>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3">
-        <v>1081</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4">
-        <v>1081</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5">
-        <v>1081</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6">
-        <v>1081</v>
-      </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7">
-        <v>1081</v>
-      </c>
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8">
-        <v>1081</v>
-      </c>
-      <c r="B8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9">
-        <v>1081</v>
-      </c>
-      <c r="B9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10">
-        <v>1081</v>
-      </c>
-      <c r="B10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11">
-        <v>1081</v>
-      </c>
-      <c r="B11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12">
-        <v>1081</v>
-      </c>
-      <c r="B12" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13">
-        <v>1081</v>
-      </c>
-      <c r="B13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14">
-        <v>1081</v>
-      </c>
-      <c r="B14" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15">
-        <v>1081</v>
-      </c>
-      <c r="B15" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16">
-        <v>1081</v>
-      </c>
-      <c r="B16" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17">
-        <v>1081</v>
-      </c>
-      <c r="B17" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18">
-        <v>1081</v>
-      </c>
-      <c r="B18" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19">
-        <v>1081</v>
-      </c>
-      <c r="B19" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" t="s">
-        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -1217,7 +1003,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1228,7 +1014,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1255,19 +1041,19 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1281,10 +1067,10 @@
         <v>1</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1298,19 +1084,19 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1324,19 +1110,19 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1350,44 +1136,44 @@
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="D6" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="D7" s="1" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="D8" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="D9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1398,16 +1184,16 @@
         <v>1</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1422,7 +1208,7 @@
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="F16" s="4"/>
     </row>
@@ -1438,7 +1224,7 @@
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="F17" s="4"/>
     </row>
@@ -1454,26 +1240,26 @@
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4" t="s">
-        <v>72</v>
+        <v>39</v>
       </c>
       <c r="F18" s="4"/>
     </row>
     <row r="22" spans="1:10">
       <c r="D22" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="E22" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="D25" s="6" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:10">
-      <c r="D26" s="5" t="s">
-        <v>76</v>
+      <c r="D26" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="31" spans="1:10">

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0A9E3D9-7C15-F34F-BA6D-92CA3B2EBE96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DA3B05B-892C-8947-AA15-F22A9396652B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="61">
   <si>
     <t>Plant</t>
   </si>
@@ -231,6 +231,9 @@
   </si>
   <si>
     <t>0215055531</t>
+  </si>
+  <si>
+    <t>0215055534</t>
   </si>
 </sst>
 </file>
@@ -860,7 +863,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E2" t="s">
         <v>22</v>

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DA3B05B-892C-8947-AA15-F22A9396652B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB341459-7C8C-5D46-B5E3-D62A00B6C2A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-4820" yWindow="-21100" windowWidth="38400" windowHeight="21100" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateASN" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,20 @@
     <sheet name="SearchASN" sheetId="6" r:id="rId6"/>
     <sheet name="BackUP" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -51,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="135">
   <si>
     <t>Plant</t>
   </si>
@@ -83,10 +96,13 @@
     <t>QA</t>
   </si>
   <si>
-    <t>VG</t>
-  </si>
-  <si>
-    <t>AJ7566-010-LT</t>
+    <t>DH6619-010-4-5.5;DH6619-010-1</t>
+  </si>
+  <si>
+    <t>12;12</t>
+  </si>
+  <si>
+    <t>6;6</t>
   </si>
   <si>
     <t>0005005401</t>
@@ -137,9 +153,21 @@
     <t>1081</t>
   </si>
   <si>
+    <t>81ASN1219QA1580</t>
+  </si>
+  <si>
+    <t>00081121920253492500;00081121920255700701;00081121920258346802;00081121920255802103</t>
+  </si>
+  <si>
     <t>N</t>
   </si>
   <si>
+    <t>81ASN1219QA9491</t>
+  </si>
+  <si>
+    <t>00081121920255149004;00081121920257937905;00081121920258260606;00081121920255540007</t>
+  </si>
+  <si>
     <t>DiversionCodeId</t>
   </si>
   <si>
@@ -170,54 +198,57 @@
     <t>Search_by_Color</t>
   </si>
   <si>
+    <t>0215055531</t>
+  </si>
+  <si>
+    <t>924156-100-S;420420-420-M;DD9293-100-7</t>
+  </si>
+  <si>
+    <t>6;6;6</t>
+  </si>
+  <si>
+    <t>924156-100-S</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>DD9293-100-7</t>
+  </si>
+  <si>
+    <t>924156-100-S@420420-420-M;DD9293-100-7</t>
+  </si>
+  <si>
+    <t>12@12;12</t>
+  </si>
+  <si>
+    <t>6@6;6</t>
+  </si>
+  <si>
+    <t>829748-010-4XL</t>
+  </si>
+  <si>
+    <t>829747-091-M-T</t>
+  </si>
+  <si>
+    <t>DD9293-100-11.5</t>
+  </si>
+  <si>
+    <t>DD9293-100-6</t>
+  </si>
+  <si>
+    <t>Item Search Backup</t>
+  </si>
+  <si>
+    <t>Apparel</t>
+  </si>
+  <si>
+    <t>Equipment</t>
+  </si>
+  <si>
     <t>Footwear</t>
   </si>
   <si>
-    <t>924156-100-S;420420-420-M;DD9293-100-7</t>
-  </si>
-  <si>
-    <t>6;6;6</t>
-  </si>
-  <si>
-    <t>924156-100-S</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>DD9293-100-7</t>
-  </si>
-  <si>
-    <t>924156-100-S@420420-420-M;DD9293-100-7</t>
-  </si>
-  <si>
-    <t>12@12;12</t>
-  </si>
-  <si>
-    <t>6@6;6</t>
-  </si>
-  <si>
-    <t>829748-010-4XL</t>
-  </si>
-  <si>
-    <t>829747-091-M-T</t>
-  </si>
-  <si>
-    <t>DD9293-100-11.5</t>
-  </si>
-  <si>
-    <t>DD9293-100-6</t>
-  </si>
-  <si>
-    <t>Item Search Backup</t>
-  </si>
-  <si>
-    <t>Apparel</t>
-  </si>
-  <si>
-    <t>Equipment</t>
-  </si>
-  <si>
     <t>VGASN1126QA8010</t>
   </si>
   <si>
@@ -230,17 +261,221 @@
     <t>VGASN1212QA2170;VGASN1212QA3730;VGASN1212QA4190;VGASN1212QA1710</t>
   </si>
   <si>
-    <t>0215055531</t>
-  </si>
-  <si>
-    <t>0215055534</t>
+    <t>SX5728-010-XS</t>
+  </si>
+  <si>
+    <t>SX5728-010-S</t>
+  </si>
+  <si>
+    <t>SX5728-010-M</t>
+  </si>
+  <si>
+    <t>SX5728-010-L</t>
+  </si>
+  <si>
+    <t>SX5728-010-XL</t>
+  </si>
+  <si>
+    <t>SX5728-100-XS</t>
+  </si>
+  <si>
+    <t>SX5728-100-S</t>
+  </si>
+  <si>
+    <t>SX5728-100-M</t>
+  </si>
+  <si>
+    <t>SX5728-100-L</t>
+  </si>
+  <si>
+    <t>SX5728-100-XL</t>
+  </si>
+  <si>
+    <t>SX5728-302-XS</t>
+  </si>
+  <si>
+    <t>SX5728-302-S</t>
+  </si>
+  <si>
+    <t>SX5728-302-M</t>
+  </si>
+  <si>
+    <t>SX5728-302-L</t>
+  </si>
+  <si>
+    <t>SX5728-302-XL</t>
+  </si>
+  <si>
+    <t>SX5728-411-XS</t>
+  </si>
+  <si>
+    <t>SX5728-411-S</t>
+  </si>
+  <si>
+    <t>SX5728-411-M</t>
+  </si>
+  <si>
+    <t>SX5728-411-L</t>
+  </si>
+  <si>
+    <t>SX5728-411-XL</t>
+  </si>
+  <si>
+    <t>SX5728-412-XS</t>
+  </si>
+  <si>
+    <t>SX5728-412-S</t>
+  </si>
+  <si>
+    <t>SX5728-412-M</t>
+  </si>
+  <si>
+    <t>SX5728-412-L</t>
+  </si>
+  <si>
+    <t>SX5728-412-XL</t>
+  </si>
+  <si>
+    <t>SX5728-448-XS</t>
+  </si>
+  <si>
+    <t>SX5728-448-S</t>
+  </si>
+  <si>
+    <t>SX5728-448-M</t>
+  </si>
+  <si>
+    <t>SX5728-448-L</t>
+  </si>
+  <si>
+    <t>SX5728-448-XL</t>
+  </si>
+  <si>
+    <t>SX5728-463-XS</t>
+  </si>
+  <si>
+    <t>SX5728-463-S</t>
+  </si>
+  <si>
+    <t>SX5728-463-M</t>
+  </si>
+  <si>
+    <t>SX5728-463-L</t>
+  </si>
+  <si>
+    <t>SX5728-463-XL</t>
+  </si>
+  <si>
+    <t>SX5728-648-XS</t>
+  </si>
+  <si>
+    <t>SX5728-648-S</t>
+  </si>
+  <si>
+    <t>SX5728-648-M</t>
+  </si>
+  <si>
+    <t>SX5728-648-L</t>
+  </si>
+  <si>
+    <t>SX5728-648-XL</t>
+  </si>
+  <si>
+    <t>SX5728-670-XS</t>
+  </si>
+  <si>
+    <t>SX5728-670-S</t>
+  </si>
+  <si>
+    <t>SX5728-670-M</t>
+  </si>
+  <si>
+    <t>SX5728-670-L</t>
+  </si>
+  <si>
+    <t>SX5728-670-XL</t>
+  </si>
+  <si>
+    <t>SX5728-702-XS</t>
+  </si>
+  <si>
+    <t>SX5728-702-S</t>
+  </si>
+  <si>
+    <t>SX5728-702-M</t>
+  </si>
+  <si>
+    <t>SX5728-702-L</t>
+  </si>
+  <si>
+    <t>SX5728-702-XL</t>
+  </si>
+  <si>
+    <t>SX5728-719-XS</t>
+  </si>
+  <si>
+    <t>SX5728-719-S</t>
+  </si>
+  <si>
+    <t>SX5728-719-M</t>
+  </si>
+  <si>
+    <t>SX5728-719-L</t>
+  </si>
+  <si>
+    <t>SX5728-719-XL</t>
+  </si>
+  <si>
+    <t>SX5854-010-XS</t>
+  </si>
+  <si>
+    <t>SX5854-010-S</t>
+  </si>
+  <si>
+    <t>SX5854-010-M</t>
+  </si>
+  <si>
+    <t>SX5854-010-L</t>
+  </si>
+  <si>
+    <t>SX5854-010-XL</t>
+  </si>
+  <si>
+    <t>SX7622-013-S</t>
+  </si>
+  <si>
+    <t>SX7622-013-M</t>
+  </si>
+  <si>
+    <t>SX7622-013-L</t>
+  </si>
+  <si>
+    <t>SX7622-013-XL</t>
+  </si>
+  <si>
+    <t>SX7622-013-2XL</t>
+  </si>
+  <si>
+    <t>SX7622-100-S</t>
+  </si>
+  <si>
+    <t>SX7622-100-2XL</t>
+  </si>
+  <si>
+    <t>SX7622-100-M</t>
+  </si>
+  <si>
+    <t>SX7622-100-L</t>
+  </si>
+  <si>
+    <t>SX7622-100-XL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -267,6 +502,12 @@
       <b/>
       <sz val="12"/>
       <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -325,7 +566,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
@@ -345,7 +586,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -731,26 +973,26 @@
       <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2">
+        <v>81</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2" t="s">
         <v>10</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="8">
-        <v>36</v>
-      </c>
-      <c r="G2" s="8">
-        <v>6</v>
+      <c r="G2" s="8" t="s">
+        <v>12</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -784,45 +1026,33 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
       <c r="D2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -832,44 +1062,67 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D1" s="11" t="s">
+      <c r="C1" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="D1" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="E1" s="12" t="s">
         <v>26</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>60</v>
+      <c r="C2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" t="s">
+        <v>30</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
         <v>28</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -890,38 +1143,38 @@
         <v>1</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -931,7 +1184,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="3" max="3" width="21.83203125" bestFit="1" customWidth="1"/>
@@ -950,22 +1203,22 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -975,11 +1228,768 @@
       <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>39</v>
+      <c r="D2" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="4"/>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3">
+        <v>1081</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4">
+        <v>1081</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5">
+        <v>1081</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6">
+        <v>1081</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7">
+        <v>1081</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8">
+        <v>1081</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9">
+        <v>1081</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10">
+        <v>1081</v>
+      </c>
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11">
+        <v>1081</v>
+      </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12">
+        <v>1081</v>
+      </c>
+      <c r="B12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13">
+        <v>1081</v>
+      </c>
+      <c r="B13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14">
+        <v>1081</v>
+      </c>
+      <c r="B14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15">
+        <v>1081</v>
+      </c>
+      <c r="B15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16">
+        <v>1081</v>
+      </c>
+      <c r="B16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17">
+        <v>1081</v>
+      </c>
+      <c r="B17" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18">
+        <v>1081</v>
+      </c>
+      <c r="B18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19">
+        <v>1081</v>
+      </c>
+      <c r="B19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20">
+        <v>1081</v>
+      </c>
+      <c r="B20" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21">
+        <v>1081</v>
+      </c>
+      <c r="B21" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22">
+        <v>1081</v>
+      </c>
+      <c r="B22" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23">
+        <v>1081</v>
+      </c>
+      <c r="B23" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24">
+        <v>1081</v>
+      </c>
+      <c r="B24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25">
+        <v>1081</v>
+      </c>
+      <c r="B25" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26">
+        <v>1081</v>
+      </c>
+      <c r="B26" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27">
+        <v>1081</v>
+      </c>
+      <c r="B27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28">
+        <v>1081</v>
+      </c>
+      <c r="B28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29">
+        <v>1081</v>
+      </c>
+      <c r="B29" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30">
+        <v>1081</v>
+      </c>
+      <c r="B30" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31">
+        <v>1081</v>
+      </c>
+      <c r="B31" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32">
+        <v>1081</v>
+      </c>
+      <c r="B32" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33">
+        <v>1081</v>
+      </c>
+      <c r="B33" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34">
+        <v>1081</v>
+      </c>
+      <c r="B34" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35">
+        <v>1081</v>
+      </c>
+      <c r="B35" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36">
+        <v>1081</v>
+      </c>
+      <c r="B36" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37">
+        <v>1081</v>
+      </c>
+      <c r="B37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38">
+        <v>1081</v>
+      </c>
+      <c r="B38" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39">
+        <v>1081</v>
+      </c>
+      <c r="B39" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40">
+        <v>1081</v>
+      </c>
+      <c r="B40" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41">
+        <v>1081</v>
+      </c>
+      <c r="B41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42">
+        <v>1081</v>
+      </c>
+      <c r="B42" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43">
+        <v>1081</v>
+      </c>
+      <c r="B43" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44">
+        <v>1081</v>
+      </c>
+      <c r="B44" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45">
+        <v>1081</v>
+      </c>
+      <c r="B45" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46">
+        <v>1081</v>
+      </c>
+      <c r="B46" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47">
+        <v>1081</v>
+      </c>
+      <c r="B47" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48">
+        <v>1081</v>
+      </c>
+      <c r="B48" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49">
+        <v>1081</v>
+      </c>
+      <c r="B49" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50">
+        <v>1081</v>
+      </c>
+      <c r="B50" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51">
+        <v>1081</v>
+      </c>
+      <c r="B51" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52">
+        <v>1081</v>
+      </c>
+      <c r="B52" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53">
+        <v>1081</v>
+      </c>
+      <c r="B53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D53" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54">
+        <v>1081</v>
+      </c>
+      <c r="B54" t="s">
+        <v>9</v>
+      </c>
+      <c r="D54" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55">
+        <v>1081</v>
+      </c>
+      <c r="B55" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56">
+        <v>1081</v>
+      </c>
+      <c r="B56" t="s">
+        <v>9</v>
+      </c>
+      <c r="D56" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57">
+        <v>1081</v>
+      </c>
+      <c r="B57" t="s">
+        <v>9</v>
+      </c>
+      <c r="D57" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58">
+        <v>1081</v>
+      </c>
+      <c r="B58" t="s">
+        <v>9</v>
+      </c>
+      <c r="D58" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59">
+        <v>1081</v>
+      </c>
+      <c r="B59" t="s">
+        <v>9</v>
+      </c>
+      <c r="D59" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60">
+        <v>1081</v>
+      </c>
+      <c r="B60" t="s">
+        <v>9</v>
+      </c>
+      <c r="D60" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61">
+        <v>1081</v>
+      </c>
+      <c r="B61" t="s">
+        <v>9</v>
+      </c>
+      <c r="D61" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62">
+        <v>1081</v>
+      </c>
+      <c r="B62" t="s">
+        <v>9</v>
+      </c>
+      <c r="D62" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63">
+        <v>1081</v>
+      </c>
+      <c r="B63" t="s">
+        <v>9</v>
+      </c>
+      <c r="D63" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64">
+        <v>1081</v>
+      </c>
+      <c r="B64" t="s">
+        <v>9</v>
+      </c>
+      <c r="D64" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65">
+        <v>1081</v>
+      </c>
+      <c r="B65" t="s">
+        <v>9</v>
+      </c>
+      <c r="D65" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66">
+        <v>1081</v>
+      </c>
+      <c r="B66" t="s">
+        <v>9</v>
+      </c>
+      <c r="D66" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67">
+        <v>1081</v>
+      </c>
+      <c r="B67" t="s">
+        <v>9</v>
+      </c>
+      <c r="D67" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68">
+        <v>1081</v>
+      </c>
+      <c r="B68" t="s">
+        <v>9</v>
+      </c>
+      <c r="D68" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69">
+        <v>1081</v>
+      </c>
+      <c r="B69" t="s">
+        <v>9</v>
+      </c>
+      <c r="D69" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70">
+        <v>1081</v>
+      </c>
+      <c r="B70" t="s">
+        <v>9</v>
+      </c>
+      <c r="D70" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71">
+        <v>1081</v>
+      </c>
+      <c r="B71" t="s">
+        <v>9</v>
+      </c>
+      <c r="D71" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -1006,7 +2016,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1017,7 +2027,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1044,19 +2054,19 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1070,10 +2080,10 @@
         <v>1</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1087,19 +2097,19 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1113,19 +2123,19 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1139,44 +2149,44 @@
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="D6" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="D7" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="D8" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="D9" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1187,16 +2197,16 @@
         <v>1</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1211,7 +2221,7 @@
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F16" s="4"/>
     </row>
@@ -1227,7 +2237,7 @@
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F17" s="4"/>
     </row>
@@ -1243,26 +2253,26 @@
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="F18" s="4"/>
     </row>
     <row r="22" spans="1:10">
       <c r="D22" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="E22" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="D25" s="6" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="D26" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="31" spans="1:10">

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB341459-7C8C-5D46-B5E3-D62A00B6C2A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACB02F0E-407B-EF41-8BC6-EE2DAB3BCCFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4820" yWindow="-21100" windowWidth="38400" windowHeight="21100" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18960" yWindow="1460" windowWidth="36000" windowHeight="22500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateASN" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="63">
   <si>
     <t>Plant</t>
   </si>
@@ -153,21 +153,12 @@
     <t>1081</t>
   </si>
   <si>
-    <t>81ASN1219QA1580</t>
-  </si>
-  <si>
     <t>00081121920253492500;00081121920255700701;00081121920258346802;00081121920255802103</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>81ASN1219QA9491</t>
-  </si>
-  <si>
-    <t>00081121920255149004;00081121920257937905;00081121920258260606;00081121920255540007</t>
-  </si>
-  <si>
     <t>DiversionCodeId</t>
   </si>
   <si>
@@ -261,221 +252,14 @@
     <t>VGASN1212QA2170;VGASN1212QA3730;VGASN1212QA4190;VGASN1212QA1710</t>
   </si>
   <si>
-    <t>SX5728-010-XS</t>
-  </si>
-  <si>
-    <t>SX5728-010-S</t>
-  </si>
-  <si>
-    <t>SX5728-010-M</t>
-  </si>
-  <si>
-    <t>SX5728-010-L</t>
-  </si>
-  <si>
-    <t>SX5728-010-XL</t>
-  </si>
-  <si>
-    <t>SX5728-100-XS</t>
-  </si>
-  <si>
-    <t>SX5728-100-S</t>
-  </si>
-  <si>
-    <t>SX5728-100-M</t>
-  </si>
-  <si>
-    <t>SX5728-100-L</t>
-  </si>
-  <si>
-    <t>SX5728-100-XL</t>
-  </si>
-  <si>
-    <t>SX5728-302-XS</t>
-  </si>
-  <si>
-    <t>SX5728-302-S</t>
-  </si>
-  <si>
-    <t>SX5728-302-M</t>
-  </si>
-  <si>
-    <t>SX5728-302-L</t>
-  </si>
-  <si>
-    <t>SX5728-302-XL</t>
-  </si>
-  <si>
-    <t>SX5728-411-XS</t>
-  </si>
-  <si>
-    <t>SX5728-411-S</t>
-  </si>
-  <si>
-    <t>SX5728-411-M</t>
-  </si>
-  <si>
-    <t>SX5728-411-L</t>
-  </si>
-  <si>
-    <t>SX5728-411-XL</t>
-  </si>
-  <si>
-    <t>SX5728-412-XS</t>
-  </si>
-  <si>
-    <t>SX5728-412-S</t>
-  </si>
-  <si>
-    <t>SX5728-412-M</t>
-  </si>
-  <si>
-    <t>SX5728-412-L</t>
-  </si>
-  <si>
-    <t>SX5728-412-XL</t>
-  </si>
-  <si>
-    <t>SX5728-448-XS</t>
-  </si>
-  <si>
-    <t>SX5728-448-S</t>
-  </si>
-  <si>
-    <t>SX5728-448-M</t>
-  </si>
-  <si>
-    <t>SX5728-448-L</t>
-  </si>
-  <si>
-    <t>SX5728-448-XL</t>
-  </si>
-  <si>
-    <t>SX5728-463-XS</t>
-  </si>
-  <si>
-    <t>SX5728-463-S</t>
-  </si>
-  <si>
-    <t>SX5728-463-M</t>
-  </si>
-  <si>
-    <t>SX5728-463-L</t>
-  </si>
-  <si>
-    <t>SX5728-463-XL</t>
-  </si>
-  <si>
-    <t>SX5728-648-XS</t>
-  </si>
-  <si>
-    <t>SX5728-648-S</t>
-  </si>
-  <si>
-    <t>SX5728-648-M</t>
-  </si>
-  <si>
-    <t>SX5728-648-L</t>
-  </si>
-  <si>
-    <t>SX5728-648-XL</t>
-  </si>
-  <si>
-    <t>SX5728-670-XS</t>
-  </si>
-  <si>
-    <t>SX5728-670-S</t>
-  </si>
-  <si>
-    <t>SX5728-670-M</t>
-  </si>
-  <si>
-    <t>SX5728-670-L</t>
-  </si>
-  <si>
-    <t>SX5728-670-XL</t>
-  </si>
-  <si>
-    <t>SX5728-702-XS</t>
-  </si>
-  <si>
-    <t>SX5728-702-S</t>
-  </si>
-  <si>
-    <t>SX5728-702-M</t>
-  </si>
-  <si>
-    <t>SX5728-702-L</t>
-  </si>
-  <si>
-    <t>SX5728-702-XL</t>
-  </si>
-  <si>
-    <t>SX5728-719-XS</t>
-  </si>
-  <si>
-    <t>SX5728-719-S</t>
-  </si>
-  <si>
-    <t>SX5728-719-M</t>
-  </si>
-  <si>
-    <t>SX5728-719-L</t>
-  </si>
-  <si>
-    <t>SX5728-719-XL</t>
-  </si>
-  <si>
-    <t>SX5854-010-XS</t>
-  </si>
-  <si>
-    <t>SX5854-010-S</t>
-  </si>
-  <si>
-    <t>SX5854-010-M</t>
-  </si>
-  <si>
-    <t>SX5854-010-L</t>
-  </si>
-  <si>
-    <t>SX5854-010-XL</t>
-  </si>
-  <si>
-    <t>SX7622-013-S</t>
-  </si>
-  <si>
-    <t>SX7622-013-M</t>
-  </si>
-  <si>
-    <t>SX7622-013-L</t>
-  </si>
-  <si>
-    <t>SX7622-013-XL</t>
-  </si>
-  <si>
-    <t>SX7622-013-2XL</t>
-  </si>
-  <si>
-    <t>SX7622-100-S</t>
-  </si>
-  <si>
-    <t>SX7622-100-2XL</t>
-  </si>
-  <si>
-    <t>SX7622-100-M</t>
-  </si>
-  <si>
-    <t>SX7622-100-L</t>
-  </si>
-  <si>
-    <t>SX7622-100-XL</t>
+    <t>0215055573</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -502,12 +286,6 @@
       <b/>
       <sz val="12"/>
       <name val="Aptos Narrow"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -566,7 +344,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
@@ -586,8 +364,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1062,26 +839,29 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <cols>
+    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="11" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1092,37 +872,17 @@
       <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2" t="s">
         <v>29</v>
-      </c>
-      <c r="D2" t="s">
-        <v>30</v>
       </c>
       <c r="E2" t="s">
         <v>23</v>
       </c>
       <c r="F2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1146,7 +906,7 @@
         <v>25</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1157,10 +917,10 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1171,10 +931,10 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1184,7 +944,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="3" max="3" width="21.83203125" bestFit="1" customWidth="1"/>
@@ -1203,22 +963,22 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" t="s">
         <v>38</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>39</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>40</v>
-      </c>
-      <c r="F1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1228,768 +988,11 @@
       <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="E2" s="4"/>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3">
-        <v>1081</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4">
-        <v>1081</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5">
-        <v>1081</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6">
-        <v>1081</v>
-      </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7">
-        <v>1081</v>
-      </c>
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8">
-        <v>1081</v>
-      </c>
-      <c r="B8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9">
-        <v>1081</v>
-      </c>
-      <c r="B9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10">
-        <v>1081</v>
-      </c>
-      <c r="B10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11">
-        <v>1081</v>
-      </c>
-      <c r="B11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12">
-        <v>1081</v>
-      </c>
-      <c r="B12" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13">
-        <v>1081</v>
-      </c>
-      <c r="B13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14">
-        <v>1081</v>
-      </c>
-      <c r="B14" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15">
-        <v>1081</v>
-      </c>
-      <c r="B15" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16">
-        <v>1081</v>
-      </c>
-      <c r="B16" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17">
-        <v>1081</v>
-      </c>
-      <c r="B17" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18">
-        <v>1081</v>
-      </c>
-      <c r="B18" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19">
-        <v>1081</v>
-      </c>
-      <c r="B19" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20">
-        <v>1081</v>
-      </c>
-      <c r="B20" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21">
-        <v>1081</v>
-      </c>
-      <c r="B21" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22">
-        <v>1081</v>
-      </c>
-      <c r="B22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23">
-        <v>1081</v>
-      </c>
-      <c r="B23" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24">
-        <v>1081</v>
-      </c>
-      <c r="B24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25">
-        <v>1081</v>
-      </c>
-      <c r="B25" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26">
-        <v>1081</v>
-      </c>
-      <c r="B26" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27">
-        <v>1081</v>
-      </c>
-      <c r="B27" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28">
-        <v>1081</v>
-      </c>
-      <c r="B28" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29">
-        <v>1081</v>
-      </c>
-      <c r="B29" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30">
-        <v>1081</v>
-      </c>
-      <c r="B30" t="s">
-        <v>9</v>
-      </c>
-      <c r="D30" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31">
-        <v>1081</v>
-      </c>
-      <c r="B31" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32">
-        <v>1081</v>
-      </c>
-      <c r="B32" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33">
-        <v>1081</v>
-      </c>
-      <c r="B33" t="s">
-        <v>9</v>
-      </c>
-      <c r="D33" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34">
-        <v>1081</v>
-      </c>
-      <c r="B34" t="s">
-        <v>9</v>
-      </c>
-      <c r="D34" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35">
-        <v>1081</v>
-      </c>
-      <c r="B35" t="s">
-        <v>9</v>
-      </c>
-      <c r="D35" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36">
-        <v>1081</v>
-      </c>
-      <c r="B36" t="s">
-        <v>9</v>
-      </c>
-      <c r="D36" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37">
-        <v>1081</v>
-      </c>
-      <c r="B37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D37" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38">
-        <v>1081</v>
-      </c>
-      <c r="B38" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39">
-        <v>1081</v>
-      </c>
-      <c r="B39" t="s">
-        <v>9</v>
-      </c>
-      <c r="D39" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40">
-        <v>1081</v>
-      </c>
-      <c r="B40" t="s">
-        <v>9</v>
-      </c>
-      <c r="D40" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41">
-        <v>1081</v>
-      </c>
-      <c r="B41" t="s">
-        <v>9</v>
-      </c>
-      <c r="D41" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42">
-        <v>1081</v>
-      </c>
-      <c r="B42" t="s">
-        <v>9</v>
-      </c>
-      <c r="D42" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43">
-        <v>1081</v>
-      </c>
-      <c r="B43" t="s">
-        <v>9</v>
-      </c>
-      <c r="D43" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44">
-        <v>1081</v>
-      </c>
-      <c r="B44" t="s">
-        <v>9</v>
-      </c>
-      <c r="D44" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
-      <c r="A45">
-        <v>1081</v>
-      </c>
-      <c r="B45" t="s">
-        <v>9</v>
-      </c>
-      <c r="D45" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
-      <c r="A46">
-        <v>1081</v>
-      </c>
-      <c r="B46" t="s">
-        <v>9</v>
-      </c>
-      <c r="D46" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47">
-        <v>1081</v>
-      </c>
-      <c r="B47" t="s">
-        <v>9</v>
-      </c>
-      <c r="D47" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
-      <c r="A48">
-        <v>1081</v>
-      </c>
-      <c r="B48" t="s">
-        <v>9</v>
-      </c>
-      <c r="D48" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4">
-      <c r="A49">
-        <v>1081</v>
-      </c>
-      <c r="B49" t="s">
-        <v>9</v>
-      </c>
-      <c r="D49" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4">
-      <c r="A50">
-        <v>1081</v>
-      </c>
-      <c r="B50" t="s">
-        <v>9</v>
-      </c>
-      <c r="D50" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4">
-      <c r="A51">
-        <v>1081</v>
-      </c>
-      <c r="B51" t="s">
-        <v>9</v>
-      </c>
-      <c r="D51" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4">
-      <c r="A52">
-        <v>1081</v>
-      </c>
-      <c r="B52" t="s">
-        <v>9</v>
-      </c>
-      <c r="D52" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4">
-      <c r="A53">
-        <v>1081</v>
-      </c>
-      <c r="B53" t="s">
-        <v>9</v>
-      </c>
-      <c r="D53" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4">
-      <c r="A54">
-        <v>1081</v>
-      </c>
-      <c r="B54" t="s">
-        <v>9</v>
-      </c>
-      <c r="D54" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4">
-      <c r="A55">
-        <v>1081</v>
-      </c>
-      <c r="B55" t="s">
-        <v>9</v>
-      </c>
-      <c r="D55" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4">
-      <c r="A56">
-        <v>1081</v>
-      </c>
-      <c r="B56" t="s">
-        <v>9</v>
-      </c>
-      <c r="D56" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4">
-      <c r="A57">
-        <v>1081</v>
-      </c>
-      <c r="B57" t="s">
-        <v>9</v>
-      </c>
-      <c r="D57" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4">
-      <c r="A58">
-        <v>1081</v>
-      </c>
-      <c r="B58" t="s">
-        <v>9</v>
-      </c>
-      <c r="D58" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4">
-      <c r="A59">
-        <v>1081</v>
-      </c>
-      <c r="B59" t="s">
-        <v>9</v>
-      </c>
-      <c r="D59" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4">
-      <c r="A60">
-        <v>1081</v>
-      </c>
-      <c r="B60" t="s">
-        <v>9</v>
-      </c>
-      <c r="D60" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4">
-      <c r="A61">
-        <v>1081</v>
-      </c>
-      <c r="B61" t="s">
-        <v>9</v>
-      </c>
-      <c r="D61" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4">
-      <c r="A62">
-        <v>1081</v>
-      </c>
-      <c r="B62" t="s">
-        <v>9</v>
-      </c>
-      <c r="D62" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4">
-      <c r="A63">
-        <v>1081</v>
-      </c>
-      <c r="B63" t="s">
-        <v>9</v>
-      </c>
-      <c r="D63" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4">
-      <c r="A64">
-        <v>1081</v>
-      </c>
-      <c r="B64" t="s">
-        <v>9</v>
-      </c>
-      <c r="D64" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4">
-      <c r="A65">
-        <v>1081</v>
-      </c>
-      <c r="B65" t="s">
-        <v>9</v>
-      </c>
-      <c r="D65" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4">
-      <c r="A66">
-        <v>1081</v>
-      </c>
-      <c r="B66" t="s">
-        <v>9</v>
-      </c>
-      <c r="D66" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4">
-      <c r="A67">
-        <v>1081</v>
-      </c>
-      <c r="B67" t="s">
-        <v>9</v>
-      </c>
-      <c r="D67" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4">
-      <c r="A68">
-        <v>1081</v>
-      </c>
-      <c r="B68" t="s">
-        <v>9</v>
-      </c>
-      <c r="D68" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4">
-      <c r="A69">
-        <v>1081</v>
-      </c>
-      <c r="B69" t="s">
-        <v>9</v>
-      </c>
-      <c r="D69" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4">
-      <c r="A70">
-        <v>1081</v>
-      </c>
-      <c r="B70" t="s">
-        <v>9</v>
-      </c>
-      <c r="D70" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4">
-      <c r="A71">
-        <v>1081</v>
-      </c>
-      <c r="B71" t="s">
-        <v>9</v>
-      </c>
-      <c r="D71" t="s">
-        <v>134</v>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -2027,7 +1030,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -2054,13 +1057,13 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>13</v>
@@ -2097,13 +1100,13 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>13</v>
@@ -2123,13 +1126,13 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>13</v>
@@ -2149,13 +1152,13 @@
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>13</v>
@@ -2166,27 +1169,27 @@
     </row>
     <row r="6" spans="1:8">
       <c r="D6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="D7" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="D8" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="D9" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -2197,16 +1200,16 @@
         <v>1</v>
       </c>
       <c r="C15" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>38</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -2221,7 +1224,7 @@
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F16" s="4"/>
     </row>
@@ -2237,7 +1240,7 @@
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F17" s="4"/>
     </row>
@@ -2253,26 +1256,26 @@
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F18" s="4"/>
     </row>
     <row r="22" spans="1:10">
       <c r="D22" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E22" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="D25" s="6" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="D26" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="31" spans="1:10">

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8EC85F0-8F6D-E244-A1AB-1B7FB3EB688F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A7E564A-A7DB-9647-99E6-1C14C78351C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="-3000" windowWidth="38400" windowHeight="21000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="-3000" windowWidth="38400" windowHeight="21000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateASN" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="60">
   <si>
     <t>Plant</t>
   </si>
@@ -230,14 +230,14 @@
     <t>VGASN1212QA2170;VGASN1212QA3730;VGASN1212QA4190;VGASN1212QA1710</t>
   </si>
   <si>
-    <t>00000010810000000724</t>
+    <t>0215055935;0215055848</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -269,6 +269,20 @@
       <b/>
       <sz val="12"/>
       <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -322,7 +336,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
@@ -345,6 +359,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -680,7 +696,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
@@ -738,7 +754,7 @@
         <v>10</v>
       </c>
       <c r="F2" s="8">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="G2" s="8">
         <v>6</v>
@@ -759,6 +775,9 @@
       <c r="F4" s="10"/>
       <c r="G4" s="10"/>
       <c r="H4" s="3"/>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="D11" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -809,6 +828,12 @@
       <c r="D2" t="s">
         <v>21</v>
       </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>21</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -820,6 +845,7 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
+    <col min="3" max="3" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -850,9 +876,10 @@
       <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="C2" s="5" t="s">
         <v>59</v>
       </c>
+      <c r="D2" s="13"/>
       <c r="E2" t="s">
         <v>21</v>
       </c>

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A7E564A-A7DB-9647-99E6-1C14C78351C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25973325-F0A5-F846-AD0B-B5EB154EE199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38400" yWindow="-3000" windowWidth="38400" windowHeight="21000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="60">
   <si>
     <t>Plant</t>
   </si>
@@ -230,7 +230,7 @@
     <t>VGASN1212QA2170;VGASN1212QA3730;VGASN1212QA4190;VGASN1212QA1710</t>
   </si>
   <si>
-    <t>0215055935;0215055848</t>
+    <t>0215056185;0215056175</t>
   </si>
 </sst>
 </file>
@@ -825,13 +825,7 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="D2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="B2" t="s">
         <v>21</v>
       </c>
     </row>

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25973325-F0A5-F846-AD0B-B5EB154EE199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F4B15D4-6E54-8142-BD59-B923BC17EFDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38400" yWindow="-3000" windowWidth="38400" windowHeight="21000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -230,7 +230,7 @@
     <t>VGASN1212QA2170;VGASN1212QA3730;VGASN1212QA4190;VGASN1212QA1710</t>
   </si>
   <si>
-    <t>0215056185;0215056175</t>
+    <t>0215056059</t>
   </si>
 </sst>
 </file>

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F4B15D4-6E54-8142-BD59-B923BC17EFDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A944571-185C-B549-B6B1-DCD36CF4042F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="-3000" windowWidth="38400" windowHeight="21000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="69840" yWindow="-5900" windowWidth="36000" windowHeight="22600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateASN" sheetId="1" r:id="rId1"/>
@@ -230,7 +230,7 @@
     <t>VGASN1212QA2170;VGASN1212QA3730;VGASN1212QA4190;VGASN1212QA1710</t>
   </si>
   <si>
-    <t>0215056059</t>
+    <t>20260202093747000000</t>
   </si>
 </sst>
 </file>
@@ -825,7 +825,7 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>21</v>
       </c>
     </row>
@@ -870,10 +870,10 @@
       <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="5"/>
+      <c r="D2" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="D2" s="13"/>
       <c r="E2" t="s">
         <v>21</v>
       </c>

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A944571-185C-B549-B6B1-DCD36CF4042F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE32BD62-628C-664B-A9A1-1A2711F0C0C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="69840" yWindow="-5900" windowWidth="36000" windowHeight="22600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateASN" sheetId="1" r:id="rId1"/>
@@ -230,7 +230,7 @@
     <t>VGASN1212QA2170;VGASN1212QA3730;VGASN1212QA4190;VGASN1212QA1710</t>
   </si>
   <si>
-    <t>20260202093747000000</t>
+    <t>0215056616</t>
   </si>
 </sst>
 </file>
@@ -870,10 +870,10 @@
       <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="13" t="s">
+      <c r="C2" s="5" t="s">
         <v>59</v>
       </c>
+      <c r="D2" s="13"/>
       <c r="E2" t="s">
         <v>21</v>
       </c>

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE32BD62-628C-664B-A9A1-1A2711F0C0C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4921F5B2-392F-1F4D-971C-28FFE195A386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateASN" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,20 @@
     <sheet name="SearchASN" sheetId="6" r:id="rId6"/>
     <sheet name="BackUP" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -51,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="63">
   <si>
     <t>Plant</t>
   </si>
@@ -83,9 +96,6 @@
     <t>QA</t>
   </si>
   <si>
-    <t>899371-091-M</t>
-  </si>
-  <si>
     <t>0005005401</t>
   </si>
   <si>
@@ -231,13 +241,25 @@
   </si>
   <si>
     <t>0215056616</t>
+  </si>
+  <si>
+    <t>FQ0462-010-M;FQ0462-010-XL;DV4349-701-3.5Y;DV4351-003-1Y</t>
+  </si>
+  <si>
+    <t>10;20;6;6</t>
+  </si>
+  <si>
+    <t>V01</t>
+  </si>
+  <si>
+    <t>3000;200;240;3900</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -283,6 +305,12 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -347,9 +375,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -361,6 +386,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -702,7 +728,7 @@
     <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="55.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -744,40 +770,40 @@
       <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="C2">
-        <v>81</v>
+      <c r="C2" t="s">
+        <v>61</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="8">
-        <v>18</v>
-      </c>
-      <c r="G2" s="8">
-        <v>6</v>
-      </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" t="s">
         <v>11</v>
       </c>
-      <c r="I2" t="s">
-        <v>12</v>
-      </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
       <c r="H3" s="3"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
       <c r="H4" s="3"/>
     </row>
     <row r="11" spans="1:9">
-      <c r="D11" s="12"/>
+      <c r="D11" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -800,33 +826,33 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" t="s">
         <v>13</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>14</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>15</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>16</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>17</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>18</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>19</v>
       </c>
-      <c r="H1" t="s">
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="D2" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -844,41 +870,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="E1" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="F1" s="10" t="s">
         <v>24</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D2" s="13"/>
+        <v>58</v>
+      </c>
+      <c r="D2" s="12"/>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -899,38 +925,38 @@
         <v>1</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
       </c>
       <c r="C2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" t="s">
         <v>29</v>
-      </c>
-      <c r="D2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -959,22 +985,22 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" t="s">
         <v>32</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>33</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>34</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>35</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>36</v>
-      </c>
-      <c r="H1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -988,10 +1014,10 @@
         <v>1</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1018,7 +1044,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1029,7 +1055,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1056,19 +1082,19 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="F1" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" t="s">
         <v>11</v>
-      </c>
-      <c r="H1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1082,10 +1108,10 @@
         <v>1</v>
       </c>
       <c r="G2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" t="s">
         <v>11</v>
-      </c>
-      <c r="H2" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1099,19 +1125,19 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="F3" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" t="s">
         <v>11</v>
-      </c>
-      <c r="H3" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1125,19 +1151,19 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" t="s">
         <v>11</v>
-      </c>
-      <c r="H4" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1151,44 +1177,44 @@
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="G5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" t="s">
         <v>11</v>
-      </c>
-      <c r="H5" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="D6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="D7" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="D8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="D9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1199,16 +1225,16 @@
         <v>1</v>
       </c>
       <c r="C15" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="E15" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="F15" s="4" t="s">
         <v>34</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1223,7 +1249,7 @@
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F16" s="4"/>
     </row>
@@ -1239,7 +1265,7 @@
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F17" s="4"/>
     </row>
@@ -1255,26 +1281,26 @@
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F18" s="4"/>
     </row>
     <row r="22" spans="1:10">
       <c r="D22" t="s">
+        <v>54</v>
+      </c>
+      <c r="E22" t="s">
         <v>55</v>
-      </c>
-      <c r="E22" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="D25" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="D26" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31" spans="1:10">

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4921F5B2-392F-1F4D-971C-28FFE195A386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2824D642-20EA-814E-B1B3-251F09FFBA8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1580" windowWidth="36000" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateASN" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="67">
   <si>
     <t>Plant</t>
   </si>
@@ -240,26 +240,38 @@
     <t>VGASN1212QA2170;VGASN1212QA3730;VGASN1212QA4190;VGASN1212QA1710</t>
   </si>
   <si>
-    <t>0215056616</t>
-  </si>
-  <si>
-    <t>FQ0462-010-M;FQ0462-010-XL;DV4349-701-3.5Y;DV4351-003-1Y</t>
-  </si>
-  <si>
-    <t>10;20;6;6</t>
-  </si>
-  <si>
-    <t>V01</t>
-  </si>
-  <si>
-    <t>3000;200;240;3900</t>
+    <t>00081062920260003101;00081062920260003102</t>
+  </si>
+  <si>
+    <t>PROD</t>
+  </si>
+  <si>
+    <t>BV6706-100-M;BV6728-010-XS;BV6728-100-M;BV6728-100-S;BV6728-100-XL;BV6728-100-XS;BV6741-657-XS;BV6741-657-S;BV6741-657-M;BV6741-657-L;BV6855-010-S;BV6855-010-XL;BV6855-100-M;BV6855-100-S;BV6855-410-S;BV6855-657-S;BV6860-010-M;BV6860-010-XL;BV6860-010-XS;BV6881-410-L;BV6881-410-M;CJ0921-011-L;CJ0921-011-M;CJ0921-011-S;CJ0921-011-XL;CJ7347-010-M;CN5342-012-L;CU2563-010-3XL;CU3218-010-L;CU3218-010-M;CU3218-010-S;CU9741-010-30;CU9741-010-36;CU9741-010-38;CU9741-012-30;CU9741-104-30;CV1991-010-XS;CW6157-010-M;CW6907-063-S;CW6907-063-XL;CZ4873-010-2XL;CZ4873-010-3XL;CZ4873-010-L;CZ4873-010-M;CZ4873-010-XL;CZ4873-010-XS;CZ4873-100-L;CZ4873-100-M;CZ4873-100-XL;CZ4873-100-XS;CZ8831-010-2XL;CZ8831-010-L;CZ8831-010-M;CZ8831-010-S;CZ8831-010-XL;CZ9241-010-XL;DA1028-010-XS;DA1028-010-S;DA1028-010-M;DA1028-010-L;DA1028-091-XS;DA1028-091-S;DA1028-091-M;DA1028-091-L;DA1099-010-L;DC3251-010-M;DC7485-687-L;DC7485-687-M;DC7485-687-S;DC7485-687-XL;DC7485-687-XS;DC7818-010-2XL;DC7818-010-3XL;DC7818-010-L;DC7818-010-M;DC7818-010-S;DC7818-010-XL;DC7818-100-2XL;DC7818-100-3XL;DC7818-100-L;DC7818-100-M;DC7818-100-S;DC7818-100-XL;DC7818-384-L</t>
+  </si>
+  <si>
+    <t>60;100;60;60;60;60;60;60;60;60;60;60;60;60;60;60;60;60;60;60;60;60;60;60;60;60;60;162;126;126;90;54;54;54;54;54;54;54;126;54;54;60;100;60;60;60;60;60;100;60;60;60;60;60;60;60;60;60;60;60;60;60;60;100;100;60;60;60;36;108;60;30;30;18;42;60;60;60;60;60;60;60;60;60</t>
+  </si>
+  <si>
+    <t>20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;18;18;18;18;18;18;18;18;18;18;18;18;18;18;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;12;12;12;6;6;6;6;20;20;20;20;20;20;20;20;20</t>
+  </si>
+  <si>
+    <t>DC7818-384-M;DC7818-384-XL;DC7818-815-2XL;DD3055-084-XS;DD3055-084-S;DD3055-084-M;DD3055-084-L;DD4747-010-2XL;DD4747-010-L;DD4747-010-M;DD4747-010-S;DD4747-010-XL;DD4747-211-L;DD4747-211-M;DD4747-211-S;DD4747-211-XL;DD4883-010-2XL;DD4883-010-L;DD4883-010-M;DD4883-010-S;DD4883-010-XL;DD4883-068-2XL;DD4883-068-L;DD4883-068-M;DD4883-068-S;DD4883-068-XL;DD4895-084-L;DD4895-084-M;DD4895-084-S;DD5004-010-S;DD5311-010-2XL;DD5311-010-L;DD5311-010-M;DD5311-010-S;DD5311-010-XL;DD5311-084-2XL;DD5311-084-L;DD5311-084-M;DD5311-084-S;DD5311-084-XL;DD5311-247-2XL;DD5311-247-L;DD5311-247-M;DD5311-247-S;DH0823-006-L;DH0823-006-M;DH0823-006-XL;DH0823-010-2XL;DH0823-010-L;DH0823-010-M;DH0823-010-S;DH0823-222-L;DH0823-222-M;DH0823-321-L;DH0823-321-M;DH0823-321-S;DH0823-321-XL;DH4791-716-L;DH4796-010-XL;DH6980-491-S;DH8112-010-2XL;DH8112-010-L;DH8112-010-M;DH8112-010-S;DH8112-010-XL;DH8112-100-L;DH8112-100-M;DH8112-100-S;DH8112-100-XL;DH8408-100-XS;DH8408-100-S;DH8408-100-M;DH8408-100-L;DH9081-010-2XL;DH9081-010-L;DH9081-010-M;DH9081-010-S;DH9081-010-XL;DH9081-011-2XL;DH9081-011-L;DH9081-011-M;DH9081-011-S;DH9081-011-XL;DJ7666-010-2XL;DJ7666-010-L;DJ7666-010-M;DJ7666-010-S;DJ7666-010-XL;DJ7666-010-XS;DJ7666-104-2XL;DJ7666-104-L;DJ7666-104-M</t>
+  </si>
+  <si>
+    <t>100;60;60;60;60;60;60;36;36;60;60;36;36;36;36;36;36;36;36;36;36;60;60;60;60;100;60;100;60;60;60;60;60;60;60;60;60;60;60;60;60;60;60;60;60;60;60;60;60;60;60;60;60;60;60;100;100;60;60;60;60;60;60;60;60;60;100;100;100;60;60;60;60;60;60;60;100;60;60;60;60;60;60;60;60;60;60;60;60;60;60;100</t>
+  </si>
+  <si>
+    <t>20;20;20;20;20;20;20;12;12;12;12;12;12;12;12;12;12;12;12;12;12;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20</t>
+  </si>
+  <si>
+    <t>V02</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -305,12 +317,6 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -364,7 +370,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
@@ -375,9 +381,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -386,7 +389,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -768,22 +770,22 @@
         <v>1081</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="F2" s="13" t="s">
+      <c r="E2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G2" t="s">
         <v>62</v>
-      </c>
-      <c r="G2" s="13" t="s">
-        <v>60</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>10</v>
@@ -793,17 +795,41 @@
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="3"/>
+      <c r="A3">
+        <v>1081</v>
+      </c>
+      <c r="B3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
       <c r="H4" s="3"/>
     </row>
     <row r="11" spans="1:9">
-      <c r="D11" s="11"/>
+      <c r="D11" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -870,22 +896,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="9" t="s">
         <v>24</v>
       </c>
     </row>
@@ -894,12 +920,12 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" s="5"/>
+      <c r="D2" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="D2" s="12"/>
       <c r="E2" t="s">
         <v>20</v>
       </c>

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2824D642-20EA-814E-B1B3-251F09FFBA8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10AA4EE5-972B-F143-B18A-F42B87696499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1580" windowWidth="36000" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateASN" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="64">
   <si>
     <t>Plant</t>
   </si>
@@ -246,32 +246,23 @@
     <t>PROD</t>
   </si>
   <si>
-    <t>BV6706-100-M;BV6728-010-XS;BV6728-100-M;BV6728-100-S;BV6728-100-XL;BV6728-100-XS;BV6741-657-XS;BV6741-657-S;BV6741-657-M;BV6741-657-L;BV6855-010-S;BV6855-010-XL;BV6855-100-M;BV6855-100-S;BV6855-410-S;BV6855-657-S;BV6860-010-M;BV6860-010-XL;BV6860-010-XS;BV6881-410-L;BV6881-410-M;CJ0921-011-L;CJ0921-011-M;CJ0921-011-S;CJ0921-011-XL;CJ7347-010-M;CN5342-012-L;CU2563-010-3XL;CU3218-010-L;CU3218-010-M;CU3218-010-S;CU9741-010-30;CU9741-010-36;CU9741-010-38;CU9741-012-30;CU9741-104-30;CV1991-010-XS;CW6157-010-M;CW6907-063-S;CW6907-063-XL;CZ4873-010-2XL;CZ4873-010-3XL;CZ4873-010-L;CZ4873-010-M;CZ4873-010-XL;CZ4873-010-XS;CZ4873-100-L;CZ4873-100-M;CZ4873-100-XL;CZ4873-100-XS;CZ8831-010-2XL;CZ8831-010-L;CZ8831-010-M;CZ8831-010-S;CZ8831-010-XL;CZ9241-010-XL;DA1028-010-XS;DA1028-010-S;DA1028-010-M;DA1028-010-L;DA1028-091-XS;DA1028-091-S;DA1028-091-M;DA1028-091-L;DA1099-010-L;DC3251-010-M;DC7485-687-L;DC7485-687-M;DC7485-687-S;DC7485-687-XL;DC7485-687-XS;DC7818-010-2XL;DC7818-010-3XL;DC7818-010-L;DC7818-010-M;DC7818-010-S;DC7818-010-XL;DC7818-100-2XL;DC7818-100-3XL;DC7818-100-L;DC7818-100-M;DC7818-100-S;DC7818-100-XL;DC7818-384-L</t>
-  </si>
-  <si>
-    <t>60;100;60;60;60;60;60;60;60;60;60;60;60;60;60;60;60;60;60;60;60;60;60;60;60;60;60;162;126;126;90;54;54;54;54;54;54;54;126;54;54;60;100;60;60;60;60;60;100;60;60;60;60;60;60;60;60;60;60;60;60;60;60;100;100;60;60;60;36;108;60;30;30;18;42;60;60;60;60;60;60;60;60;60</t>
-  </si>
-  <si>
-    <t>20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;18;18;18;18;18;18;18;18;18;18;18;18;18;18;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;12;12;12;6;6;6;6;20;20;20;20;20;20;20;20;20</t>
-  </si>
-  <si>
-    <t>DC7818-384-M;DC7818-384-XL;DC7818-815-2XL;DD3055-084-XS;DD3055-084-S;DD3055-084-M;DD3055-084-L;DD4747-010-2XL;DD4747-010-L;DD4747-010-M;DD4747-010-S;DD4747-010-XL;DD4747-211-L;DD4747-211-M;DD4747-211-S;DD4747-211-XL;DD4883-010-2XL;DD4883-010-L;DD4883-010-M;DD4883-010-S;DD4883-010-XL;DD4883-068-2XL;DD4883-068-L;DD4883-068-M;DD4883-068-S;DD4883-068-XL;DD4895-084-L;DD4895-084-M;DD4895-084-S;DD5004-010-S;DD5311-010-2XL;DD5311-010-L;DD5311-010-M;DD5311-010-S;DD5311-010-XL;DD5311-084-2XL;DD5311-084-L;DD5311-084-M;DD5311-084-S;DD5311-084-XL;DD5311-247-2XL;DD5311-247-L;DD5311-247-M;DD5311-247-S;DH0823-006-L;DH0823-006-M;DH0823-006-XL;DH0823-010-2XL;DH0823-010-L;DH0823-010-M;DH0823-010-S;DH0823-222-L;DH0823-222-M;DH0823-321-L;DH0823-321-M;DH0823-321-S;DH0823-321-XL;DH4791-716-L;DH4796-010-XL;DH6980-491-S;DH8112-010-2XL;DH8112-010-L;DH8112-010-M;DH8112-010-S;DH8112-010-XL;DH8112-100-L;DH8112-100-M;DH8112-100-S;DH8112-100-XL;DH8408-100-XS;DH8408-100-S;DH8408-100-M;DH8408-100-L;DH9081-010-2XL;DH9081-010-L;DH9081-010-M;DH9081-010-S;DH9081-010-XL;DH9081-011-2XL;DH9081-011-L;DH9081-011-M;DH9081-011-S;DH9081-011-XL;DJ7666-010-2XL;DJ7666-010-L;DJ7666-010-M;DJ7666-010-S;DJ7666-010-XL;DJ7666-010-XS;DJ7666-104-2XL;DJ7666-104-L;DJ7666-104-M</t>
-  </si>
-  <si>
-    <t>100;60;60;60;60;60;60;36;36;60;60;36;36;36;36;36;36;36;36;36;36;60;60;60;60;100;60;100;60;60;60;60;60;60;60;60;60;60;60;60;60;60;60;60;60;60;60;60;60;60;60;60;60;60;60;100;100;60;60;60;60;60;60;60;60;60;100;100;100;60;60;60;60;60;60;60;100;60;60;60;60;60;60;60;60;60;60;60;60;60;60;100</t>
-  </si>
-  <si>
-    <t>20;20;20;20;20;20;20;12;12;12;12;12;12;12;12;12;12;12;12;12;12;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20;20</t>
-  </si>
-  <si>
-    <t>V02</t>
+    <t>FQ0462-010-M;FQ0462-010-XL;DV4349-701-3.5Y;DV4351-003-1Y</t>
+  </si>
+  <si>
+    <t>3010;220;246;3906</t>
+  </si>
+  <si>
+    <t>10;20;6;6</t>
+  </si>
+  <si>
+    <t>PV01</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -303,13 +294,6 @@
       <b/>
       <sz val="12"/>
       <name val="Aptos Narrow"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -370,7 +354,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
@@ -381,14 +365,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -773,7 +753,7 @@
         <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -795,41 +775,58 @@
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3">
-        <v>1081</v>
-      </c>
-      <c r="B3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F3" t="s">
-        <v>64</v>
-      </c>
-      <c r="G3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I3" t="s">
-        <v>11</v>
-      </c>
+      <c r="E3"/>
+      <c r="F3"/>
+      <c r="G3"/>
+      <c r="H3" s="3"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
+      <c r="E4"/>
+      <c r="F4"/>
+      <c r="G4"/>
       <c r="H4" s="3"/>
     </row>
+    <row r="5" spans="1:9">
+      <c r="E5"/>
+      <c r="F5"/>
+      <c r="G5"/>
+      <c r="H5" s="3"/>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="E6"/>
+      <c r="F6"/>
+      <c r="G6"/>
+      <c r="H6" s="3"/>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="E7"/>
+      <c r="F7"/>
+      <c r="G7"/>
+      <c r="H7" s="3"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="E8"/>
+      <c r="F8"/>
+      <c r="G8"/>
+      <c r="H8" s="3"/>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="E9"/>
+      <c r="F9"/>
+      <c r="G9"/>
+      <c r="H9" s="3"/>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="E10"/>
+      <c r="F10"/>
+      <c r="G10"/>
+      <c r="H10" s="3"/>
+    </row>
     <row r="11" spans="1:9">
-      <c r="D11" s="10"/>
+      <c r="E11"/>
+      <c r="F11"/>
+      <c r="G11"/>
+      <c r="H11" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -896,22 +893,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="8" t="s">
         <v>24</v>
       </c>
     </row>
@@ -923,7 +920,7 @@
         <v>59</v>
       </c>
       <c r="C2" s="5"/>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="9" t="s">
         <v>58</v>
       </c>
       <c r="E2" t="s">

--- a/J30/Input_files/WorkSheet.xlsx
+++ b/J30/Input_files/WorkSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10AA4EE5-972B-F143-B18A-F42B87696499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BE7B879-CDEF-E148-9259-BAF85A33BAA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18060" yWindow="-21000" windowWidth="19200" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateASN" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="77">
   <si>
     <t>Plant</t>
   </si>
@@ -246,16 +246,55 @@
     <t>PROD</t>
   </si>
   <si>
-    <t>FQ0462-010-M;FQ0462-010-XL;DV4349-701-3.5Y;DV4351-003-1Y</t>
-  </si>
-  <si>
-    <t>3010;220;246;3906</t>
-  </si>
-  <si>
-    <t>10;20;6;6</t>
-  </si>
-  <si>
-    <t>PV01</t>
+    <t>V8</t>
+  </si>
+  <si>
+    <t>FQ0516-072-XL;FQ1151-490-2XL;FQ1637-010-L;DV4349-701-4Y;DV4349-701-5Y;DV4349-701-6Y;DV4351-003-1.5Y;DV4351-402-3Y;DV4351-402-4Y;DV4351-402-5Y;DV4351-402-6Y</t>
+  </si>
+  <si>
+    <t>DV4351-701-1Y;DV4351-701-2Y;DV4351-701-2.5Y;DV4351-701-3Y;DV4351-701-3.5Y;DV4351-701-4Y;DV4351-701-5Y;DV4351-701-6Y;DV5456-002-3.5Y;DV5456-002-4Y;DV5456-002-5Y;DV5456-002-6Y;DV5456-002-6.5Y;DV5456-002-7Y;DV5456-008-3.5Y</t>
+  </si>
+  <si>
+    <t>DV5456-008-4Y;DV5456-008-5Y;DV5456-008-6Y;DV5456-008-6.5Y;DV5456-008-7Y;DV5456-012-3.5Y;DV5456-012-4Y;DV5456-012-5Y;DV5456-012-6Y;DV5456-012-6.5Y;DV5456-012-7Y;DV5456-104-3.5Y;DV5456-104-4Y;DV5456-104-5Y;DV5456-104-6Y</t>
+  </si>
+  <si>
+    <t>DV5456-104-6.5Y;DV5456-104-7Y;DV5456-105-3.5Y;DV5456-105-4Y;DV5456-105-5Y;DV5456-105-6Y;DV5456-105-6.5Y;DV5456-105-7Y;DV5456-106-3.5Y;DV5456-106-4Y;DV5456-106-5Y;DV5456-106-6Y;DV5456-106-6.5Y;DV5456-106-7Y;DV5456-131-3.5Y</t>
+  </si>
+  <si>
+    <t>DV5456-131-4Y;DV5456-131-5Y;DV5456-131-6Y;DV5456-131-6.5Y;DV5456-131-7Y;DV5456-133-3.5Y;DV5456-133-4Y;DV5456-133-5Y;DV5456-133-6Y;DV5456-133-6.5Y;DV5456-133-7Y;DV5456-135-3.5Y;DV5456-600-3.5Y;DV5456-600-4Y;DV5456-600-5Y</t>
+  </si>
+  <si>
+    <t>DV5456-600-6Y;DV5456-600-6.5Y;DV5456-600-7Y;DV5456-601-3.5Y;DV5456-601-4Y;DV5456-601-5Y;DV5456-601-6.5Y;DV5457-002-10.5C;DV5457-002-11C;DV5457-002-11.5C;DV5457-002-12C;DV5457-002-12.5C;DV5457-002-13C;DV5457-002-13.5C;DV5457-002-1Y</t>
+  </si>
+  <si>
+    <t>DV5457-002-1.5Y;DV5457-002-2Y;DV5457-002-2.5Y;DV5457-002-3Y;DV5457-008-11C;DV5457-008-11.5C;DV5457-008-12C;DV5457-008-12.5C;DV5457-008-13C;DV5457-008-13.5C;DV5457-008-1Y;DV5457-008-1.5Y;DV5457-008-2Y;DV5457-008-2.5Y;DV5457-008-3Y</t>
+  </si>
+  <si>
+    <t>DV5457-012-10.5C;DV5457-012-11C;DV5457-012-11.5C;DV5457-012-12C;DV5457-012-12.5C;DV5457-012-13C;DV5457-012-13.5C;DV5457-012-1Y;DV5457-012-1.5Y;DV5457-012-2Y;DV5457-012-2.5Y;DV5457-012-3Y;DV5457-104-10.5C;DV5457-104-11C;DV5457-104-11.5C</t>
+  </si>
+  <si>
+    <t>DV5457-104-12C;DV5457-104-12.5C;DV5457-104-13C;DV5457-104-13.5C;DV5457-104-1Y;DV5457-104-1.5Y;DV5457-104-2Y;DV5457-104-2.5Y;DV5457-104-3Y;DV5457-105-10.5C;DV5457-105-11C;DV5457-105-11.5C;DV5457-105-12C;DV5457-105-12.5C;DV5457-105-13C</t>
+  </si>
+  <si>
+    <t>DV5457-105-13.5C;DV5457-105-1Y;DV5457-105-1.5Y;DV5457-105-2Y;DV5457-105-2.5Y;DV5457-105-3Y;DV5457-106-10.5C;DV5457-106-11C;DV5457-106-11.5C;DV5457-106-12C;DV5457-106-12.5C;DV5457-106-13C;FJ4864-100-3;FJ4864-100-4;FN0536-017-L</t>
+  </si>
+  <si>
+    <t>800;800;400;240;240;120;120;120;120;120;120</t>
+  </si>
+  <si>
+    <t>120;120;120;120;120;120;120;120;120;120;120;120;120;120;120</t>
+  </si>
+  <si>
+    <t>120;120;120;120;120;120;120;120;120;120;120;120;400;400;400</t>
+  </si>
+  <si>
+    <t>20;20;20;6;6;6;6;6;6;6;6</t>
+  </si>
+  <si>
+    <t>6;6;6;6;6;6;6;6;6;6;6;6;6;6;6</t>
+  </si>
+  <si>
+    <t>6;6;6;6;6;6;6;6;6;6;6;6;20;20;20</t>
   </si>
 </sst>
 </file>
@@ -753,19 +792,19 @@
         <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="G2" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>10</v>
@@ -775,58 +814,265 @@
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="E3"/>
-      <c r="F3"/>
-      <c r="G3"/>
-      <c r="H3" s="3"/>
+      <c r="A3">
+        <v>1081</v>
+      </c>
+      <c r="B3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="E4"/>
-      <c r="F4"/>
-      <c r="G4"/>
-      <c r="H4" s="3"/>
+      <c r="A4">
+        <v>1081</v>
+      </c>
+      <c r="B4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" t="s">
+        <v>72</v>
+      </c>
+      <c r="G4" t="s">
+        <v>75</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="E5"/>
-      <c r="F5"/>
-      <c r="G5"/>
-      <c r="H5" s="3"/>
+      <c r="A5">
+        <v>1081</v>
+      </c>
+      <c r="B5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F5" t="s">
+        <v>72</v>
+      </c>
+      <c r="G5" t="s">
+        <v>75</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="E6"/>
-      <c r="F6"/>
-      <c r="G6"/>
-      <c r="H6" s="3"/>
+      <c r="A6">
+        <v>1081</v>
+      </c>
+      <c r="B6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>65</v>
+      </c>
+      <c r="F6" t="s">
+        <v>72</v>
+      </c>
+      <c r="G6" t="s">
+        <v>75</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I6" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="E7"/>
-      <c r="F7"/>
-      <c r="G7"/>
-      <c r="H7" s="3"/>
+      <c r="A7">
+        <v>1081</v>
+      </c>
+      <c r="B7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>66</v>
+      </c>
+      <c r="F7" t="s">
+        <v>72</v>
+      </c>
+      <c r="G7" t="s">
+        <v>75</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="E8"/>
-      <c r="F8"/>
-      <c r="G8"/>
-      <c r="H8" s="3"/>
+      <c r="A8">
+        <v>1081</v>
+      </c>
+      <c r="B8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G8" t="s">
+        <v>75</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I8" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="E9"/>
-      <c r="F9"/>
-      <c r="G9"/>
-      <c r="H9" s="3"/>
+      <c r="A9">
+        <v>1081</v>
+      </c>
+      <c r="B9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F9" t="s">
+        <v>72</v>
+      </c>
+      <c r="G9" t="s">
+        <v>75</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I9" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="E10"/>
-      <c r="F10"/>
-      <c r="G10"/>
-      <c r="H10" s="3"/>
+      <c r="A10">
+        <v>1081</v>
+      </c>
+      <c r="B10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10" t="s">
+        <v>69</v>
+      </c>
+      <c r="F10" t="s">
+        <v>72</v>
+      </c>
+      <c r="G10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I10" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="E11"/>
-      <c r="F11"/>
-      <c r="G11"/>
-      <c r="H11" s="3"/>
+      <c r="A11">
+        <v>1081</v>
+      </c>
+      <c r="B11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11" t="s">
+        <v>70</v>
+      </c>
+      <c r="F11" t="s">
+        <v>73</v>
+      </c>
+      <c r="G11" t="s">
+        <v>76</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I11" t="s">
+        <v>11</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
